--- a/ECON13310/Q_GDP.xlsx
+++ b/ECON13310/Q_GDP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oscar Galvez Soriano\Documents\Teaching\ECON13310\Lectures\L15\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galve\Documents\UChicago\EDE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11773890-B6AF-4D5F-8817-2C41485211BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7852F80E-2D58-432A-AA4F-C4DDFE3771E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{939685C7-5FFB-4D41-92E6-3A3F06F690F5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{939685C7-5FFB-4D41-92E6-3A3F06F690F5}"/>
   </bookViews>
   <sheets>
     <sheet name="GDP" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="15">
   <si>
     <t>Year</t>
   </si>
@@ -92,7 +92,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -109,8 +109,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -129,6 +141,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -142,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -163,6 +181,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -181,9 +202,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -221,7 +242,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -327,7 +348,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -469,7 +490,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -477,838 +498,838 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA92532F-D379-41E8-8B04-BF2611B59A16}">
-  <dimension ref="A1:I309"/>
-  <sheetFormatPr defaultColWidth="20.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AJ318"/>
+  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" customWidth="1"/>
-    <col min="7" max="7" width="2.42578125" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" customWidth="1"/>
+    <col min="7" max="7" width="2.44140625" customWidth="1"/>
     <col min="161" max="161" width="5" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="163" max="163" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="165" max="165" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="163" max="163" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="164" max="164" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="166" max="166" width="7" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="168" max="168" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="169" max="169" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="170" max="170" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="172" max="172" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="173" max="173" width="16.28515625" customWidth="1"/>
+    <col min="167" max="167" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="168" max="168" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="169" max="169" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="170" max="170" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="16.33203125" customWidth="1"/>
     <col min="417" max="417" width="5" bestFit="1" customWidth="1"/>
-    <col min="418" max="418" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="419" max="419" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="420" max="420" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="421" max="421" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="418" max="418" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="419" max="419" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="420" max="420" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="421" max="421" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="422" max="422" width="7" bestFit="1" customWidth="1"/>
-    <col min="423" max="423" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="424" max="424" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="425" max="425" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="426" max="426" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="427" max="427" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="428" max="428" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="429" max="429" width="16.28515625" customWidth="1"/>
+    <col min="423" max="423" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="424" max="424" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="425" max="425" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="426" max="426" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="427" max="427" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="428" max="428" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="429" max="429" width="16.33203125" customWidth="1"/>
     <col min="673" max="673" width="5" bestFit="1" customWidth="1"/>
-    <col min="674" max="674" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="675" max="675" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="676" max="676" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="677" max="677" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="674" max="674" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="675" max="675" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="676" max="676" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="677" max="677" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="678" max="678" width="7" bestFit="1" customWidth="1"/>
-    <col min="679" max="679" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="680" max="680" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="681" max="681" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="682" max="682" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="683" max="683" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="684" max="684" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="685" max="685" width="16.28515625" customWidth="1"/>
+    <col min="679" max="679" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="680" max="680" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="681" max="681" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="682" max="682" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="683" max="683" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="684" max="684" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="685" max="685" width="16.33203125" customWidth="1"/>
     <col min="929" max="929" width="5" bestFit="1" customWidth="1"/>
-    <col min="930" max="930" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="931" max="931" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="932" max="932" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="933" max="933" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="930" max="930" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="931" max="931" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="932" max="932" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="933" max="933" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="934" max="934" width="7" bestFit="1" customWidth="1"/>
-    <col min="935" max="935" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="936" max="936" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="937" max="937" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="938" max="938" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="939" max="939" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="940" max="940" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="941" max="941" width="16.28515625" customWidth="1"/>
+    <col min="935" max="935" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="936" max="936" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="937" max="937" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="938" max="938" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="939" max="939" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="940" max="940" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="941" max="941" width="16.33203125" customWidth="1"/>
     <col min="1185" max="1185" width="5" bestFit="1" customWidth="1"/>
-    <col min="1186" max="1186" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="1187" max="1187" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="1188" max="1188" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="1189" max="1189" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1186" max="1186" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1187" max="1187" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1188" max="1188" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="1189" max="1189" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="1190" max="1190" width="7" bestFit="1" customWidth="1"/>
-    <col min="1191" max="1191" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="1192" max="1192" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="1193" max="1193" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="1194" max="1194" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="1195" max="1195" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="1196" max="1196" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="1197" max="1197" width="16.28515625" customWidth="1"/>
+    <col min="1191" max="1191" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1192" max="1192" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1193" max="1193" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1194" max="1194" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1195" max="1195" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1196" max="1196" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1197" max="1197" width="16.33203125" customWidth="1"/>
     <col min="1441" max="1441" width="5" bestFit="1" customWidth="1"/>
-    <col min="1442" max="1442" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="1443" max="1443" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="1444" max="1444" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="1445" max="1445" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1442" max="1442" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1443" max="1443" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1444" max="1444" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="1445" max="1445" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="1446" max="1446" width="7" bestFit="1" customWidth="1"/>
-    <col min="1447" max="1447" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="1448" max="1448" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="1449" max="1449" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="1450" max="1450" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="1451" max="1451" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="1452" max="1452" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="1453" max="1453" width="16.28515625" customWidth="1"/>
+    <col min="1447" max="1447" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1448" max="1448" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1449" max="1449" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1450" max="1450" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1451" max="1451" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1452" max="1452" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1453" max="1453" width="16.33203125" customWidth="1"/>
     <col min="1697" max="1697" width="5" bestFit="1" customWidth="1"/>
-    <col min="1698" max="1698" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="1699" max="1699" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="1700" max="1700" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="1701" max="1701" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1698" max="1698" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1699" max="1699" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1700" max="1700" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="1701" max="1701" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="1702" max="1702" width="7" bestFit="1" customWidth="1"/>
-    <col min="1703" max="1703" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="1704" max="1704" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="1705" max="1705" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="1706" max="1706" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="1707" max="1707" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="1708" max="1708" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="1709" max="1709" width="16.28515625" customWidth="1"/>
+    <col min="1703" max="1703" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1704" max="1704" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1705" max="1705" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1706" max="1706" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1707" max="1707" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1708" max="1708" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1709" max="1709" width="16.33203125" customWidth="1"/>
     <col min="1953" max="1953" width="5" bestFit="1" customWidth="1"/>
-    <col min="1954" max="1954" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="1955" max="1955" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="1956" max="1956" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="1957" max="1957" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1954" max="1954" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1955" max="1955" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1956" max="1956" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="1957" max="1957" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="1958" max="1958" width="7" bestFit="1" customWidth="1"/>
-    <col min="1959" max="1959" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="1960" max="1960" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="1961" max="1961" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="1962" max="1962" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="1963" max="1963" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="1964" max="1964" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="1965" max="1965" width="16.28515625" customWidth="1"/>
+    <col min="1959" max="1959" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1960" max="1960" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1961" max="1961" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1962" max="1962" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1963" max="1963" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1964" max="1964" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1965" max="1965" width="16.33203125" customWidth="1"/>
     <col min="2209" max="2209" width="5" bestFit="1" customWidth="1"/>
-    <col min="2210" max="2210" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2211" max="2211" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2212" max="2212" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2213" max="2213" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2210" max="2210" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2211" max="2211" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2212" max="2212" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2213" max="2213" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2214" max="2214" width="7" bestFit="1" customWidth="1"/>
-    <col min="2215" max="2215" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2216" max="2216" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2217" max="2217" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2218" max="2218" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2219" max="2219" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2220" max="2220" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2221" max="2221" width="16.28515625" customWidth="1"/>
+    <col min="2215" max="2215" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2216" max="2216" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2217" max="2217" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2218" max="2218" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2219" max="2219" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2220" max="2220" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2221" max="2221" width="16.33203125" customWidth="1"/>
     <col min="2465" max="2465" width="5" bestFit="1" customWidth="1"/>
-    <col min="2466" max="2466" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2467" max="2467" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2468" max="2468" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2469" max="2469" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2466" max="2466" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2467" max="2467" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2468" max="2468" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2469" max="2469" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2470" max="2470" width="7" bestFit="1" customWidth="1"/>
-    <col min="2471" max="2471" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2472" max="2472" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2473" max="2473" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2474" max="2474" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2475" max="2475" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2476" max="2476" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2477" max="2477" width="16.28515625" customWidth="1"/>
+    <col min="2471" max="2471" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2472" max="2472" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2473" max="2473" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2474" max="2474" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2475" max="2475" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2476" max="2476" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2477" max="2477" width="16.33203125" customWidth="1"/>
     <col min="2721" max="2721" width="5" bestFit="1" customWidth="1"/>
-    <col min="2722" max="2722" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2723" max="2723" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2724" max="2724" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2725" max="2725" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2722" max="2722" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2723" max="2723" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2724" max="2724" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2725" max="2725" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2726" max="2726" width="7" bestFit="1" customWidth="1"/>
-    <col min="2727" max="2727" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2728" max="2728" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2729" max="2729" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2730" max="2730" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2731" max="2731" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2732" max="2732" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2733" max="2733" width="16.28515625" customWidth="1"/>
+    <col min="2727" max="2727" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2728" max="2728" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2729" max="2729" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2730" max="2730" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2731" max="2731" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2732" max="2732" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2733" max="2733" width="16.33203125" customWidth="1"/>
     <col min="2977" max="2977" width="5" bestFit="1" customWidth="1"/>
-    <col min="2978" max="2978" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2979" max="2979" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2980" max="2980" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2981" max="2981" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2978" max="2978" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2979" max="2979" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2980" max="2980" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2981" max="2981" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2982" max="2982" width="7" bestFit="1" customWidth="1"/>
-    <col min="2983" max="2983" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2984" max="2984" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2985" max="2985" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2986" max="2986" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2987" max="2987" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2988" max="2988" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2989" max="2989" width="16.28515625" customWidth="1"/>
+    <col min="2983" max="2983" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2984" max="2984" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2985" max="2985" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2986" max="2986" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2987" max="2987" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2988" max="2988" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2989" max="2989" width="16.33203125" customWidth="1"/>
     <col min="3233" max="3233" width="5" bestFit="1" customWidth="1"/>
-    <col min="3234" max="3234" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3235" max="3235" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3236" max="3236" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="3237" max="3237" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3234" max="3234" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="3235" max="3235" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3236" max="3236" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3237" max="3237" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3238" max="3238" width="7" bestFit="1" customWidth="1"/>
-    <col min="3239" max="3239" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3240" max="3240" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3241" max="3241" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3242" max="3242" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3243" max="3243" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3244" max="3244" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3245" max="3245" width="16.28515625" customWidth="1"/>
+    <col min="3239" max="3239" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3240" max="3240" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3241" max="3241" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3242" max="3242" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3243" max="3243" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3244" max="3244" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3245" max="3245" width="16.33203125" customWidth="1"/>
     <col min="3489" max="3489" width="5" bestFit="1" customWidth="1"/>
-    <col min="3490" max="3490" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3491" max="3491" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3492" max="3492" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="3493" max="3493" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3490" max="3490" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="3491" max="3491" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3492" max="3492" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3493" max="3493" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3494" max="3494" width="7" bestFit="1" customWidth="1"/>
-    <col min="3495" max="3495" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3496" max="3496" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3497" max="3497" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3498" max="3498" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3499" max="3499" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3500" max="3500" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3501" max="3501" width="16.28515625" customWidth="1"/>
+    <col min="3495" max="3495" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3496" max="3496" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3497" max="3497" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3498" max="3498" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3499" max="3499" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3500" max="3500" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3501" max="3501" width="16.33203125" customWidth="1"/>
     <col min="3745" max="3745" width="5" bestFit="1" customWidth="1"/>
-    <col min="3746" max="3746" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3747" max="3747" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3748" max="3748" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="3749" max="3749" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3746" max="3746" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="3747" max="3747" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3748" max="3748" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3749" max="3749" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3750" max="3750" width="7" bestFit="1" customWidth="1"/>
-    <col min="3751" max="3751" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3752" max="3752" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3753" max="3753" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3754" max="3754" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3755" max="3755" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3756" max="3756" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3757" max="3757" width="16.28515625" customWidth="1"/>
+    <col min="3751" max="3751" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3752" max="3752" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3753" max="3753" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3754" max="3754" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3755" max="3755" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3756" max="3756" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3757" max="3757" width="16.33203125" customWidth="1"/>
     <col min="4001" max="4001" width="5" bestFit="1" customWidth="1"/>
-    <col min="4002" max="4002" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4003" max="4003" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4004" max="4004" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4005" max="4005" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4002" max="4002" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4003" max="4003" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4004" max="4004" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4005" max="4005" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4006" max="4006" width="7" bestFit="1" customWidth="1"/>
-    <col min="4007" max="4007" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4008" max="4008" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="4009" max="4009" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4010" max="4010" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="4011" max="4011" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4012" max="4012" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4013" max="4013" width="16.28515625" customWidth="1"/>
+    <col min="4007" max="4007" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4008" max="4008" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4009" max="4009" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4010" max="4010" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4011" max="4011" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4012" max="4012" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4013" max="4013" width="16.33203125" customWidth="1"/>
     <col min="4257" max="4257" width="5" bestFit="1" customWidth="1"/>
-    <col min="4258" max="4258" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4259" max="4259" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4260" max="4260" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4261" max="4261" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4258" max="4258" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4259" max="4259" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4260" max="4260" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4261" max="4261" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4262" max="4262" width="7" bestFit="1" customWidth="1"/>
-    <col min="4263" max="4263" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4264" max="4264" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="4265" max="4265" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4266" max="4266" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="4267" max="4267" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4268" max="4268" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4269" max="4269" width="16.28515625" customWidth="1"/>
+    <col min="4263" max="4263" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4264" max="4264" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4265" max="4265" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4266" max="4266" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4267" max="4267" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4268" max="4268" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4269" max="4269" width="16.33203125" customWidth="1"/>
     <col min="4513" max="4513" width="5" bestFit="1" customWidth="1"/>
-    <col min="4514" max="4514" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4515" max="4515" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4516" max="4516" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4517" max="4517" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4514" max="4514" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4515" max="4515" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4516" max="4516" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4517" max="4517" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4518" max="4518" width="7" bestFit="1" customWidth="1"/>
-    <col min="4519" max="4519" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4520" max="4520" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="4521" max="4521" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4522" max="4522" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="4523" max="4523" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4524" max="4524" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4525" max="4525" width="16.28515625" customWidth="1"/>
+    <col min="4519" max="4519" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4520" max="4520" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4521" max="4521" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4522" max="4522" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4523" max="4523" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4524" max="4524" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4525" max="4525" width="16.33203125" customWidth="1"/>
     <col min="4769" max="4769" width="5" bestFit="1" customWidth="1"/>
-    <col min="4770" max="4770" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4771" max="4771" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4772" max="4772" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4773" max="4773" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4770" max="4770" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4771" max="4771" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4772" max="4772" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4773" max="4773" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4774" max="4774" width="7" bestFit="1" customWidth="1"/>
-    <col min="4775" max="4775" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4776" max="4776" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="4777" max="4777" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4778" max="4778" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="4779" max="4779" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4780" max="4780" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4781" max="4781" width="16.28515625" customWidth="1"/>
+    <col min="4775" max="4775" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4776" max="4776" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4777" max="4777" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4778" max="4778" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4779" max="4779" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4780" max="4780" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4781" max="4781" width="16.33203125" customWidth="1"/>
     <col min="5025" max="5025" width="5" bestFit="1" customWidth="1"/>
-    <col min="5026" max="5026" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5027" max="5027" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5028" max="5028" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="5029" max="5029" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5026" max="5026" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="5027" max="5027" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5028" max="5028" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="5029" max="5029" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5030" max="5030" width="7" bestFit="1" customWidth="1"/>
-    <col min="5031" max="5031" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5032" max="5032" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5033" max="5033" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5034" max="5034" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5035" max="5035" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5036" max="5036" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5037" max="5037" width="16.28515625" customWidth="1"/>
+    <col min="5031" max="5031" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5032" max="5032" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5033" max="5033" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5034" max="5034" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5035" max="5035" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5036" max="5036" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5037" max="5037" width="16.33203125" customWidth="1"/>
     <col min="5281" max="5281" width="5" bestFit="1" customWidth="1"/>
-    <col min="5282" max="5282" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5283" max="5283" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5284" max="5284" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="5285" max="5285" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5282" max="5282" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="5283" max="5283" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5284" max="5284" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="5285" max="5285" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5286" max="5286" width="7" bestFit="1" customWidth="1"/>
-    <col min="5287" max="5287" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5288" max="5288" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5289" max="5289" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5290" max="5290" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5291" max="5291" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5292" max="5292" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5293" max="5293" width="16.28515625" customWidth="1"/>
+    <col min="5287" max="5287" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5288" max="5288" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5289" max="5289" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5290" max="5290" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5291" max="5291" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5292" max="5292" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5293" max="5293" width="16.33203125" customWidth="1"/>
     <col min="5537" max="5537" width="5" bestFit="1" customWidth="1"/>
-    <col min="5538" max="5538" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5539" max="5539" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5540" max="5540" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="5541" max="5541" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5538" max="5538" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="5539" max="5539" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5540" max="5540" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="5541" max="5541" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5542" max="5542" width="7" bestFit="1" customWidth="1"/>
-    <col min="5543" max="5543" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5544" max="5544" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5545" max="5545" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5546" max="5546" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5547" max="5547" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5548" max="5548" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5549" max="5549" width="16.28515625" customWidth="1"/>
+    <col min="5543" max="5543" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5544" max="5544" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5545" max="5545" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5546" max="5546" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5547" max="5547" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5548" max="5548" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5549" max="5549" width="16.33203125" customWidth="1"/>
     <col min="5793" max="5793" width="5" bestFit="1" customWidth="1"/>
-    <col min="5794" max="5794" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5795" max="5795" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5796" max="5796" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="5797" max="5797" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5794" max="5794" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="5795" max="5795" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5796" max="5796" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="5797" max="5797" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5798" max="5798" width="7" bestFit="1" customWidth="1"/>
-    <col min="5799" max="5799" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5800" max="5800" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5801" max="5801" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5802" max="5802" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5803" max="5803" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5804" max="5804" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5805" max="5805" width="16.28515625" customWidth="1"/>
+    <col min="5799" max="5799" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5800" max="5800" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5801" max="5801" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5802" max="5802" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5803" max="5803" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5804" max="5804" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5805" max="5805" width="16.33203125" customWidth="1"/>
     <col min="6049" max="6049" width="5" bestFit="1" customWidth="1"/>
-    <col min="6050" max="6050" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6051" max="6051" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6052" max="6052" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6053" max="6053" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6050" max="6050" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="6051" max="6051" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6052" max="6052" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6053" max="6053" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="6054" max="6054" width="7" bestFit="1" customWidth="1"/>
-    <col min="6055" max="6055" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6056" max="6056" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6057" max="6057" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="6058" max="6058" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6059" max="6059" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6060" max="6060" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6061" max="6061" width="16.28515625" customWidth="1"/>
+    <col min="6055" max="6055" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="6056" max="6056" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6057" max="6057" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="6058" max="6058" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6059" max="6059" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6060" max="6060" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6061" max="6061" width="16.33203125" customWidth="1"/>
     <col min="6305" max="6305" width="5" bestFit="1" customWidth="1"/>
-    <col min="6306" max="6306" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6307" max="6307" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6308" max="6308" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6309" max="6309" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6306" max="6306" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="6307" max="6307" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6308" max="6308" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6309" max="6309" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="6310" max="6310" width="7" bestFit="1" customWidth="1"/>
-    <col min="6311" max="6311" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6312" max="6312" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6313" max="6313" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="6314" max="6314" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6315" max="6315" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6316" max="6316" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6317" max="6317" width="16.28515625" customWidth="1"/>
+    <col min="6311" max="6311" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="6312" max="6312" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6313" max="6313" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="6314" max="6314" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6315" max="6315" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6316" max="6316" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6317" max="6317" width="16.33203125" customWidth="1"/>
     <col min="6561" max="6561" width="5" bestFit="1" customWidth="1"/>
-    <col min="6562" max="6562" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6563" max="6563" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6564" max="6564" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6565" max="6565" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6562" max="6562" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="6563" max="6563" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6564" max="6564" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6565" max="6565" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="6566" max="6566" width="7" bestFit="1" customWidth="1"/>
-    <col min="6567" max="6567" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6568" max="6568" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6569" max="6569" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="6570" max="6570" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6571" max="6571" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6572" max="6572" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6573" max="6573" width="16.28515625" customWidth="1"/>
+    <col min="6567" max="6567" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="6568" max="6568" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6569" max="6569" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="6570" max="6570" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6571" max="6571" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6572" max="6572" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6573" max="6573" width="16.33203125" customWidth="1"/>
     <col min="6817" max="6817" width="5" bestFit="1" customWidth="1"/>
-    <col min="6818" max="6818" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6819" max="6819" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6820" max="6820" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6821" max="6821" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6818" max="6818" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="6819" max="6819" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6820" max="6820" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6821" max="6821" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="6822" max="6822" width="7" bestFit="1" customWidth="1"/>
-    <col min="6823" max="6823" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6824" max="6824" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6825" max="6825" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="6826" max="6826" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6827" max="6827" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6828" max="6828" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6829" max="6829" width="16.28515625" customWidth="1"/>
+    <col min="6823" max="6823" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="6824" max="6824" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6825" max="6825" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="6826" max="6826" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6827" max="6827" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6828" max="6828" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6829" max="6829" width="16.33203125" customWidth="1"/>
     <col min="7073" max="7073" width="5" bestFit="1" customWidth="1"/>
-    <col min="7074" max="7074" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7075" max="7075" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7076" max="7076" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="7077" max="7077" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7074" max="7074" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="7075" max="7075" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7076" max="7076" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="7077" max="7077" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="7078" max="7078" width="7" bestFit="1" customWidth="1"/>
-    <col min="7079" max="7079" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7080" max="7080" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7081" max="7081" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="7082" max="7082" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7083" max="7083" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7084" max="7084" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7085" max="7085" width="16.28515625" customWidth="1"/>
+    <col min="7079" max="7079" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7080" max="7080" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7081" max="7081" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="7082" max="7082" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7083" max="7083" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7084" max="7084" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7085" max="7085" width="16.33203125" customWidth="1"/>
     <col min="7329" max="7329" width="5" bestFit="1" customWidth="1"/>
-    <col min="7330" max="7330" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7331" max="7331" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7332" max="7332" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="7333" max="7333" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7330" max="7330" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="7331" max="7331" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7332" max="7332" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="7333" max="7333" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="7334" max="7334" width="7" bestFit="1" customWidth="1"/>
-    <col min="7335" max="7335" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7336" max="7336" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7337" max="7337" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="7338" max="7338" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7339" max="7339" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7340" max="7340" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7341" max="7341" width="16.28515625" customWidth="1"/>
+    <col min="7335" max="7335" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7336" max="7336" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7337" max="7337" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="7338" max="7338" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7339" max="7339" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7340" max="7340" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7341" max="7341" width="16.33203125" customWidth="1"/>
     <col min="7585" max="7585" width="5" bestFit="1" customWidth="1"/>
-    <col min="7586" max="7586" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7587" max="7587" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7588" max="7588" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="7589" max="7589" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7586" max="7586" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="7587" max="7587" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7588" max="7588" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="7589" max="7589" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="7590" max="7590" width="7" bestFit="1" customWidth="1"/>
-    <col min="7591" max="7591" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7592" max="7592" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7593" max="7593" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="7594" max="7594" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7595" max="7595" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7596" max="7596" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7597" max="7597" width="16.28515625" customWidth="1"/>
+    <col min="7591" max="7591" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7592" max="7592" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7593" max="7593" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="7594" max="7594" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7595" max="7595" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7596" max="7596" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7597" max="7597" width="16.33203125" customWidth="1"/>
     <col min="7841" max="7841" width="5" bestFit="1" customWidth="1"/>
-    <col min="7842" max="7842" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="7843" max="7843" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7844" max="7844" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="7845" max="7845" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7842" max="7842" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="7843" max="7843" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7844" max="7844" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="7845" max="7845" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="7846" max="7846" width="7" bestFit="1" customWidth="1"/>
-    <col min="7847" max="7847" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7848" max="7848" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7849" max="7849" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="7850" max="7850" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7851" max="7851" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7852" max="7852" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7853" max="7853" width="16.28515625" customWidth="1"/>
+    <col min="7847" max="7847" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7848" max="7848" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7849" max="7849" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="7850" max="7850" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7851" max="7851" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7852" max="7852" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7853" max="7853" width="16.33203125" customWidth="1"/>
     <col min="8097" max="8097" width="5" bestFit="1" customWidth="1"/>
-    <col min="8098" max="8098" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8099" max="8099" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8100" max="8100" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="8101" max="8101" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8098" max="8098" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8099" max="8099" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8100" max="8100" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="8101" max="8101" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="8102" max="8102" width="7" bestFit="1" customWidth="1"/>
-    <col min="8103" max="8103" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="8104" max="8104" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="8105" max="8105" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8106" max="8106" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8107" max="8107" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8108" max="8108" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8109" max="8109" width="16.28515625" customWidth="1"/>
+    <col min="8103" max="8103" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8104" max="8104" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="8105" max="8105" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8106" max="8106" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8107" max="8107" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8108" max="8108" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8109" max="8109" width="16.33203125" customWidth="1"/>
     <col min="8353" max="8353" width="5" bestFit="1" customWidth="1"/>
-    <col min="8354" max="8354" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8355" max="8355" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8356" max="8356" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="8357" max="8357" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8354" max="8354" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8355" max="8355" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8356" max="8356" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="8357" max="8357" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="8358" max="8358" width="7" bestFit="1" customWidth="1"/>
-    <col min="8359" max="8359" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="8360" max="8360" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="8361" max="8361" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8362" max="8362" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8363" max="8363" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8364" max="8364" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8365" max="8365" width="16.28515625" customWidth="1"/>
+    <col min="8359" max="8359" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8360" max="8360" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="8361" max="8361" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8362" max="8362" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8363" max="8363" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8364" max="8364" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8365" max="8365" width="16.33203125" customWidth="1"/>
     <col min="8609" max="8609" width="5" bestFit="1" customWidth="1"/>
-    <col min="8610" max="8610" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8611" max="8611" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8612" max="8612" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="8613" max="8613" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8610" max="8610" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8611" max="8611" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8612" max="8612" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="8613" max="8613" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="8614" max="8614" width="7" bestFit="1" customWidth="1"/>
-    <col min="8615" max="8615" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="8616" max="8616" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="8617" max="8617" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8618" max="8618" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8619" max="8619" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8620" max="8620" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8621" max="8621" width="16.28515625" customWidth="1"/>
+    <col min="8615" max="8615" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8616" max="8616" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="8617" max="8617" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8618" max="8618" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8619" max="8619" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8620" max="8620" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8621" max="8621" width="16.33203125" customWidth="1"/>
     <col min="8865" max="8865" width="5" bestFit="1" customWidth="1"/>
-    <col min="8866" max="8866" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8867" max="8867" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8868" max="8868" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="8869" max="8869" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8866" max="8866" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8867" max="8867" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8868" max="8868" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="8869" max="8869" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="8870" max="8870" width="7" bestFit="1" customWidth="1"/>
-    <col min="8871" max="8871" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="8872" max="8872" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="8873" max="8873" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8874" max="8874" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="8875" max="8875" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8876" max="8876" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8877" max="8877" width="16.28515625" customWidth="1"/>
+    <col min="8871" max="8871" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8872" max="8872" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="8873" max="8873" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8874" max="8874" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8875" max="8875" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8876" max="8876" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8877" max="8877" width="16.33203125" customWidth="1"/>
     <col min="9121" max="9121" width="5" bestFit="1" customWidth="1"/>
-    <col min="9122" max="9122" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="9123" max="9123" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9124" max="9124" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="9125" max="9125" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9122" max="9122" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9123" max="9123" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9124" max="9124" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="9125" max="9125" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="9126" max="9126" width="7" bestFit="1" customWidth="1"/>
-    <col min="9127" max="9127" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9128" max="9128" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9129" max="9129" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9130" max="9130" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9131" max="9131" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9132" max="9132" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9133" max="9133" width="16.28515625" customWidth="1"/>
+    <col min="9127" max="9127" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="9128" max="9128" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9129" max="9129" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9130" max="9130" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9131" max="9131" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="9132" max="9132" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9133" max="9133" width="16.33203125" customWidth="1"/>
     <col min="9377" max="9377" width="5" bestFit="1" customWidth="1"/>
-    <col min="9378" max="9378" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="9379" max="9379" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9380" max="9380" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="9381" max="9381" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9378" max="9378" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9379" max="9379" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9380" max="9380" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="9381" max="9381" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="9382" max="9382" width="7" bestFit="1" customWidth="1"/>
-    <col min="9383" max="9383" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9384" max="9384" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9385" max="9385" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9386" max="9386" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9387" max="9387" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9388" max="9388" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9389" max="9389" width="16.28515625" customWidth="1"/>
+    <col min="9383" max="9383" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="9384" max="9384" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9385" max="9385" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9386" max="9386" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9387" max="9387" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="9388" max="9388" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9389" max="9389" width="16.33203125" customWidth="1"/>
     <col min="9633" max="9633" width="5" bestFit="1" customWidth="1"/>
-    <col min="9634" max="9634" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="9635" max="9635" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9636" max="9636" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="9637" max="9637" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9634" max="9634" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9635" max="9635" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9636" max="9636" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="9637" max="9637" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="9638" max="9638" width="7" bestFit="1" customWidth="1"/>
-    <col min="9639" max="9639" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9640" max="9640" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9641" max="9641" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9642" max="9642" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9643" max="9643" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9644" max="9644" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9645" max="9645" width="16.28515625" customWidth="1"/>
+    <col min="9639" max="9639" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="9640" max="9640" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9641" max="9641" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9642" max="9642" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9643" max="9643" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="9644" max="9644" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9645" max="9645" width="16.33203125" customWidth="1"/>
     <col min="9889" max="9889" width="5" bestFit="1" customWidth="1"/>
-    <col min="9890" max="9890" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="9891" max="9891" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9892" max="9892" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="9893" max="9893" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9890" max="9890" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9891" max="9891" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9892" max="9892" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="9893" max="9893" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="9894" max="9894" width="7" bestFit="1" customWidth="1"/>
-    <col min="9895" max="9895" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9896" max="9896" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9897" max="9897" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9898" max="9898" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9899" max="9899" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9900" max="9900" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9901" max="9901" width="16.28515625" customWidth="1"/>
+    <col min="9895" max="9895" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="9896" max="9896" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9897" max="9897" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9898" max="9898" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9899" max="9899" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="9900" max="9900" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9901" max="9901" width="16.33203125" customWidth="1"/>
     <col min="10145" max="10145" width="5" bestFit="1" customWidth="1"/>
-    <col min="10146" max="10146" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="10147" max="10147" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10148" max="10148" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="10149" max="10149" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10146" max="10146" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10147" max="10147" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10148" max="10148" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="10149" max="10149" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="10150" max="10150" width="7" bestFit="1" customWidth="1"/>
-    <col min="10151" max="10151" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10152" max="10152" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10153" max="10153" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="10154" max="10154" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10155" max="10155" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10156" max="10156" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10157" max="10157" width="16.28515625" customWidth="1"/>
+    <col min="10151" max="10151" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="10152" max="10152" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10153" max="10153" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="10154" max="10154" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10155" max="10155" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10156" max="10156" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10157" max="10157" width="16.33203125" customWidth="1"/>
     <col min="10401" max="10401" width="5" bestFit="1" customWidth="1"/>
-    <col min="10402" max="10402" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="10403" max="10403" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10404" max="10404" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="10405" max="10405" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10402" max="10402" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10403" max="10403" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10404" max="10404" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="10405" max="10405" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="10406" max="10406" width="7" bestFit="1" customWidth="1"/>
-    <col min="10407" max="10407" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10408" max="10408" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10409" max="10409" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="10410" max="10410" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10411" max="10411" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10412" max="10412" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10413" max="10413" width="16.28515625" customWidth="1"/>
+    <col min="10407" max="10407" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="10408" max="10408" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10409" max="10409" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="10410" max="10410" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10411" max="10411" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10412" max="10412" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10413" max="10413" width="16.33203125" customWidth="1"/>
     <col min="10657" max="10657" width="5" bestFit="1" customWidth="1"/>
-    <col min="10658" max="10658" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="10659" max="10659" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10660" max="10660" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="10661" max="10661" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10658" max="10658" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10659" max="10659" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10660" max="10660" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="10661" max="10661" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="10662" max="10662" width="7" bestFit="1" customWidth="1"/>
-    <col min="10663" max="10663" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10664" max="10664" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10665" max="10665" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="10666" max="10666" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10667" max="10667" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10668" max="10668" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10669" max="10669" width="16.28515625" customWidth="1"/>
+    <col min="10663" max="10663" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="10664" max="10664" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10665" max="10665" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="10666" max="10666" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10667" max="10667" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10668" max="10668" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10669" max="10669" width="16.33203125" customWidth="1"/>
     <col min="10913" max="10913" width="5" bestFit="1" customWidth="1"/>
-    <col min="10914" max="10914" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="10915" max="10915" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10916" max="10916" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="10917" max="10917" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10914" max="10914" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10915" max="10915" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10916" max="10916" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="10917" max="10917" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="10918" max="10918" width="7" bestFit="1" customWidth="1"/>
-    <col min="10919" max="10919" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10920" max="10920" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10921" max="10921" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="10922" max="10922" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10923" max="10923" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10924" max="10924" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10925" max="10925" width="16.28515625" customWidth="1"/>
+    <col min="10919" max="10919" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="10920" max="10920" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10921" max="10921" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="10922" max="10922" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10923" max="10923" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10924" max="10924" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10925" max="10925" width="16.33203125" customWidth="1"/>
     <col min="11169" max="11169" width="5" bestFit="1" customWidth="1"/>
-    <col min="11170" max="11170" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11171" max="11171" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11172" max="11172" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="11173" max="11173" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11170" max="11170" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11171" max="11171" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11172" max="11172" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11173" max="11173" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="11174" max="11174" width="7" bestFit="1" customWidth="1"/>
-    <col min="11175" max="11175" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11176" max="11176" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="11177" max="11177" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="11178" max="11178" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11179" max="11179" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11180" max="11180" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11181" max="11181" width="16.28515625" customWidth="1"/>
+    <col min="11175" max="11175" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11176" max="11176" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="11177" max="11177" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="11178" max="11178" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11179" max="11179" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11180" max="11180" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11181" max="11181" width="16.33203125" customWidth="1"/>
     <col min="11425" max="11425" width="5" bestFit="1" customWidth="1"/>
-    <col min="11426" max="11426" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11427" max="11427" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11428" max="11428" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="11429" max="11429" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11426" max="11426" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11427" max="11427" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11428" max="11428" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11429" max="11429" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="11430" max="11430" width="7" bestFit="1" customWidth="1"/>
-    <col min="11431" max="11431" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11432" max="11432" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="11433" max="11433" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="11434" max="11434" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11435" max="11435" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11436" max="11436" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11437" max="11437" width="16.28515625" customWidth="1"/>
+    <col min="11431" max="11431" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11432" max="11432" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="11433" max="11433" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="11434" max="11434" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11435" max="11435" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11436" max="11436" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11437" max="11437" width="16.33203125" customWidth="1"/>
     <col min="11681" max="11681" width="5" bestFit="1" customWidth="1"/>
-    <col min="11682" max="11682" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11683" max="11683" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11684" max="11684" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="11685" max="11685" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11682" max="11682" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11683" max="11683" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11684" max="11684" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11685" max="11685" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="11686" max="11686" width="7" bestFit="1" customWidth="1"/>
-    <col min="11687" max="11687" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11688" max="11688" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="11689" max="11689" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="11690" max="11690" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11691" max="11691" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11692" max="11692" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11693" max="11693" width="16.28515625" customWidth="1"/>
+    <col min="11687" max="11687" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11688" max="11688" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="11689" max="11689" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="11690" max="11690" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11691" max="11691" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11692" max="11692" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11693" max="11693" width="16.33203125" customWidth="1"/>
     <col min="11937" max="11937" width="5" bestFit="1" customWidth="1"/>
-    <col min="11938" max="11938" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11939" max="11939" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11940" max="11940" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="11941" max="11941" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11938" max="11938" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11939" max="11939" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11940" max="11940" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11941" max="11941" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="11942" max="11942" width="7" bestFit="1" customWidth="1"/>
-    <col min="11943" max="11943" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11944" max="11944" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="11945" max="11945" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="11946" max="11946" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11947" max="11947" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11948" max="11948" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11949" max="11949" width="16.28515625" customWidth="1"/>
+    <col min="11943" max="11943" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11944" max="11944" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="11945" max="11945" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="11946" max="11946" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11947" max="11947" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11948" max="11948" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11949" max="11949" width="16.33203125" customWidth="1"/>
     <col min="12193" max="12193" width="5" bestFit="1" customWidth="1"/>
-    <col min="12194" max="12194" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="12195" max="12195" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12196" max="12196" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="12197" max="12197" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="12194" max="12194" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="12195" max="12195" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="12196" max="12196" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="12197" max="12197" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="12198" max="12198" width="7" bestFit="1" customWidth="1"/>
-    <col min="12199" max="12199" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12200" max="12200" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="12201" max="12201" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12202" max="12202" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="12203" max="12203" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="12204" max="12204" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12205" max="12205" width="16.28515625" customWidth="1"/>
+    <col min="12199" max="12199" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="12200" max="12200" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="12201" max="12201" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="12202" max="12202" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="12203" max="12203" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12204" max="12204" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12205" max="12205" width="16.33203125" customWidth="1"/>
     <col min="12449" max="12449" width="5" bestFit="1" customWidth="1"/>
-    <col min="12450" max="12450" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="12451" max="12451" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12452" max="12452" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="12453" max="12453" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="12450" max="12450" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="12451" max="12451" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="12452" max="12452" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="12453" max="12453" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="12454" max="12454" width="7" bestFit="1" customWidth="1"/>
-    <col min="12455" max="12455" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12456" max="12456" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="12457" max="12457" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12458" max="12458" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="12459" max="12459" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="12460" max="12460" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12461" max="12461" width="16.28515625" customWidth="1"/>
+    <col min="12455" max="12455" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="12456" max="12456" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="12457" max="12457" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="12458" max="12458" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="12459" max="12459" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12460" max="12460" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12461" max="12461" width="16.33203125" customWidth="1"/>
     <col min="12705" max="12705" width="5" bestFit="1" customWidth="1"/>
-    <col min="12706" max="12706" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="12707" max="12707" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12708" max="12708" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="12709" max="12709" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="12706" max="12706" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="12707" max="12707" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="12708" max="12708" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="12709" max="12709" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="12710" max="12710" width="7" bestFit="1" customWidth="1"/>
-    <col min="12711" max="12711" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12712" max="12712" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="12713" max="12713" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12714" max="12714" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="12715" max="12715" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="12716" max="12716" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12717" max="12717" width="16.28515625" customWidth="1"/>
+    <col min="12711" max="12711" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="12712" max="12712" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="12713" max="12713" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="12714" max="12714" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="12715" max="12715" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12716" max="12716" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12717" max="12717" width="16.33203125" customWidth="1"/>
     <col min="12961" max="12961" width="5" bestFit="1" customWidth="1"/>
-    <col min="12962" max="12962" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="12963" max="12963" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12964" max="12964" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="12965" max="12965" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="12962" max="12962" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="12963" max="12963" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="12964" max="12964" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="12965" max="12965" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="12966" max="12966" width="7" bestFit="1" customWidth="1"/>
-    <col min="12967" max="12967" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12968" max="12968" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="12969" max="12969" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12970" max="12970" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="12971" max="12971" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="12972" max="12972" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12973" max="12973" width="16.28515625" customWidth="1"/>
+    <col min="12967" max="12967" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="12968" max="12968" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="12969" max="12969" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="12970" max="12970" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="12971" max="12971" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12972" max="12972" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12973" max="12973" width="16.33203125" customWidth="1"/>
     <col min="13217" max="13217" width="5" bestFit="1" customWidth="1"/>
-    <col min="13218" max="13218" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="13219" max="13219" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="13220" max="13220" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="13221" max="13221" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13218" max="13218" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="13219" max="13219" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="13220" max="13220" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="13221" max="13221" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="13222" max="13222" width="7" bestFit="1" customWidth="1"/>
-    <col min="13223" max="13223" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13224" max="13224" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="13225" max="13225" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="13226" max="13226" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13227" max="13227" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="13228" max="13228" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13229" max="13229" width="16.28515625" customWidth="1"/>
+    <col min="13223" max="13223" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13224" max="13224" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="13225" max="13225" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13226" max="13226" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13227" max="13227" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13228" max="13228" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13229" max="13229" width="16.33203125" customWidth="1"/>
     <col min="13473" max="13473" width="5" bestFit="1" customWidth="1"/>
-    <col min="13474" max="13474" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="13475" max="13475" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="13476" max="13476" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="13477" max="13477" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13474" max="13474" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="13475" max="13475" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="13476" max="13476" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="13477" max="13477" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="13478" max="13478" width="7" bestFit="1" customWidth="1"/>
-    <col min="13479" max="13479" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13480" max="13480" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="13481" max="13481" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="13482" max="13482" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13483" max="13483" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="13484" max="13484" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13485" max="13485" width="16.28515625" customWidth="1"/>
+    <col min="13479" max="13479" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13480" max="13480" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="13481" max="13481" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13482" max="13482" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13483" max="13483" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13484" max="13484" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13485" max="13485" width="16.33203125" customWidth="1"/>
     <col min="13729" max="13729" width="5" bestFit="1" customWidth="1"/>
-    <col min="13730" max="13730" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="13731" max="13731" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="13732" max="13732" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="13733" max="13733" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13730" max="13730" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="13731" max="13731" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="13732" max="13732" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="13733" max="13733" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="13734" max="13734" width="7" bestFit="1" customWidth="1"/>
-    <col min="13735" max="13735" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13736" max="13736" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="13737" max="13737" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="13738" max="13738" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13739" max="13739" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="13740" max="13740" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13741" max="13741" width="16.28515625" customWidth="1"/>
+    <col min="13735" max="13735" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13736" max="13736" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="13737" max="13737" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13738" max="13738" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13739" max="13739" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13740" max="13740" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13741" max="13741" width="16.33203125" customWidth="1"/>
     <col min="13985" max="13985" width="5" bestFit="1" customWidth="1"/>
-    <col min="13986" max="13986" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="13987" max="13987" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="13988" max="13988" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="13989" max="13989" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13986" max="13986" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="13987" max="13987" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="13988" max="13988" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="13989" max="13989" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="13990" max="13990" width="7" bestFit="1" customWidth="1"/>
-    <col min="13991" max="13991" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13992" max="13992" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="13993" max="13993" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="13994" max="13994" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13995" max="13995" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="13996" max="13996" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13997" max="13997" width="16.28515625" customWidth="1"/>
+    <col min="13991" max="13991" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13992" max="13992" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="13993" max="13993" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13994" max="13994" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13995" max="13995" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13996" max="13996" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13997" max="13997" width="16.33203125" customWidth="1"/>
     <col min="14241" max="14241" width="5" bestFit="1" customWidth="1"/>
-    <col min="14242" max="14242" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="14243" max="14243" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14244" max="14244" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="14245" max="14245" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14242" max="14242" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="14243" max="14243" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="14244" max="14244" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="14245" max="14245" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="14246" max="14246" width="7" bestFit="1" customWidth="1"/>
-    <col min="14247" max="14247" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14248" max="14248" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="14249" max="14249" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14250" max="14250" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="14251" max="14251" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14252" max="14252" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="14253" max="14253" width="16.28515625" customWidth="1"/>
+    <col min="14247" max="14247" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="14248" max="14248" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="14249" max="14249" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14250" max="14250" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14251" max="14251" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14252" max="14252" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14253" max="14253" width="16.33203125" customWidth="1"/>
     <col min="14497" max="14497" width="5" bestFit="1" customWidth="1"/>
-    <col min="14498" max="14498" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="14499" max="14499" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14500" max="14500" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="14501" max="14501" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14498" max="14498" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="14499" max="14499" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="14500" max="14500" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="14501" max="14501" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="14502" max="14502" width="7" bestFit="1" customWidth="1"/>
-    <col min="14503" max="14503" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14504" max="14504" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="14505" max="14505" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14506" max="14506" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="14507" max="14507" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14508" max="14508" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="14509" max="14509" width="16.28515625" customWidth="1"/>
+    <col min="14503" max="14503" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="14504" max="14504" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="14505" max="14505" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14506" max="14506" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14507" max="14507" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14508" max="14508" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14509" max="14509" width="16.33203125" customWidth="1"/>
     <col min="14753" max="14753" width="5" bestFit="1" customWidth="1"/>
-    <col min="14754" max="14754" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="14755" max="14755" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14756" max="14756" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="14757" max="14757" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14754" max="14754" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="14755" max="14755" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="14756" max="14756" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="14757" max="14757" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="14758" max="14758" width="7" bestFit="1" customWidth="1"/>
-    <col min="14759" max="14759" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14760" max="14760" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="14761" max="14761" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14762" max="14762" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="14763" max="14763" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14764" max="14764" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="14765" max="14765" width="16.28515625" customWidth="1"/>
+    <col min="14759" max="14759" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="14760" max="14760" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="14761" max="14761" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14762" max="14762" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14763" max="14763" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14764" max="14764" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14765" max="14765" width="16.33203125" customWidth="1"/>
     <col min="15009" max="15009" width="5" bestFit="1" customWidth="1"/>
-    <col min="15010" max="15010" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="15011" max="15011" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="15012" max="15012" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="15013" max="15013" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15010" max="15010" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15011" max="15011" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="15012" max="15012" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="15013" max="15013" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="15014" max="15014" width="7" bestFit="1" customWidth="1"/>
-    <col min="15015" max="15015" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="15016" max="15016" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15017" max="15017" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15018" max="15018" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15019" max="15019" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15020" max="15020" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="15021" max="15021" width="16.28515625" customWidth="1"/>
+    <col min="15015" max="15015" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="15016" max="15016" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15017" max="15017" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="15018" max="15018" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="15019" max="15019" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15020" max="15020" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15021" max="15021" width="16.33203125" customWidth="1"/>
     <col min="15265" max="15265" width="5" bestFit="1" customWidth="1"/>
-    <col min="15266" max="15266" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="15267" max="15267" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="15268" max="15268" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="15269" max="15269" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15266" max="15266" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15267" max="15267" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="15268" max="15268" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="15269" max="15269" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="15270" max="15270" width="7" bestFit="1" customWidth="1"/>
-    <col min="15271" max="15271" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="15272" max="15272" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15273" max="15273" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15274" max="15274" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15275" max="15275" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15276" max="15276" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="15277" max="15277" width="16.28515625" customWidth="1"/>
+    <col min="15271" max="15271" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="15272" max="15272" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15273" max="15273" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="15274" max="15274" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="15275" max="15275" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15276" max="15276" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15277" max="15277" width="16.33203125" customWidth="1"/>
     <col min="15521" max="15521" width="5" bestFit="1" customWidth="1"/>
-    <col min="15522" max="15522" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="15523" max="15523" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="15524" max="15524" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="15525" max="15525" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15522" max="15522" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15523" max="15523" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="15524" max="15524" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="15525" max="15525" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="15526" max="15526" width="7" bestFit="1" customWidth="1"/>
-    <col min="15527" max="15527" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="15528" max="15528" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15529" max="15529" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15530" max="15530" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15531" max="15531" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15532" max="15532" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="15533" max="15533" width="16.28515625" customWidth="1"/>
+    <col min="15527" max="15527" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="15528" max="15528" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15529" max="15529" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="15530" max="15530" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="15531" max="15531" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15532" max="15532" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15533" max="15533" width="16.33203125" customWidth="1"/>
     <col min="15777" max="15777" width="5" bestFit="1" customWidth="1"/>
-    <col min="15778" max="15778" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="15779" max="15779" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="15780" max="15780" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="15781" max="15781" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15778" max="15778" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15779" max="15779" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="15780" max="15780" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="15781" max="15781" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="15782" max="15782" width="7" bestFit="1" customWidth="1"/>
-    <col min="15783" max="15783" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="15784" max="15784" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15785" max="15785" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15786" max="15786" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15787" max="15787" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15788" max="15788" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="15789" max="15789" width="16.28515625" customWidth="1"/>
+    <col min="15783" max="15783" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="15784" max="15784" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15785" max="15785" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="15786" max="15786" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="15787" max="15787" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15788" max="15788" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15789" max="15789" width="16.33203125" customWidth="1"/>
     <col min="16033" max="16033" width="5" bestFit="1" customWidth="1"/>
-    <col min="16034" max="16034" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="16035" max="16035" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="16036" max="16036" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="16037" max="16037" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="16034" max="16034" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="16035" max="16035" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="16036" max="16036" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="16037" max="16037" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="16038" max="16038" width="7" bestFit="1" customWidth="1"/>
-    <col min="16039" max="16039" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="16040" max="16040" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="16041" max="16041" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16042" max="16042" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="16043" max="16043" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="16044" max="16044" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16045" max="16045" width="16.28515625" customWidth="1"/>
+    <col min="16039" max="16039" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="16040" max="16040" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="16041" max="16041" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="16042" max="16042" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="16043" max="16043" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="16044" max="16044" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="16045" max="16045" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1353,7 @@
       </c>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1947</v>
       </c>
@@ -1358,7 +1379,7 @@
         <v>-1.9419999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
@@ -1384,7 +1405,7 @@
         <v>-2.8730000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
         <v>5</v>
@@ -1410,7 +1431,7 @@
         <v>-3.427</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
         <v>6</v>
@@ -1434,7 +1455,7 @@
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1948</v>
       </c>
@@ -1456,7 +1477,7 @@
         <v>33.229999999999563</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="3" t="s">
         <v>4</v>
@@ -1476,7 +1497,7 @@
         <v>37.008000000000266</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="3" t="s">
         <v>5</v>
@@ -1496,7 +1517,7 @@
         <v>13.079999999999927</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="3" t="s">
         <v>6</v>
@@ -1516,7 +1537,7 @@
         <v>2.5940000000000509</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1949</v>
       </c>
@@ -1538,7 +1559,7 @@
         <v>-31.557000000000244</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="3" t="s">
         <v>4</v>
@@ -1558,7 +1579,7 @@
         <v>-7.6789999999996326</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="3" t="s">
         <v>5</v>
@@ -1578,7 +1599,7 @@
         <v>23.295999999999822</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3" t="s">
         <v>6</v>
@@ -1598,7 +1619,7 @@
         <v>-19.072000000000116</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>1950</v>
       </c>
@@ -1620,7 +1641,7 @@
         <v>88.751999999999953</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="3" t="s">
         <v>4</v>
@@ -1640,7 +1661,7 @@
         <v>71.577999999999975</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="3" t="s">
         <v>5</v>
@@ -1660,7 +1681,7 @@
         <v>93.445000000000164</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -1680,7 +1701,7 @@
         <v>48.086999999999989</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>1951</v>
       </c>
@@ -1702,7 +1723,7 @@
         <v>34.753000000000156</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
         <v>4</v>
@@ -1722,7 +1743,7 @@
         <v>44.93100000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="3" t="s">
         <v>5</v>
@@ -1742,7 +1763,7 @@
         <v>54.360999999999876</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="3" t="s">
         <v>6</v>
@@ -1762,7 +1783,7 @@
         <v>5.8969999999999345</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>1952</v>
       </c>
@@ -1784,7 +1805,7 @@
         <v>28.798000000000229</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="3" t="s">
         <v>4</v>
@@ -1804,7 +1825,7 @@
         <v>5.8460000000000036</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
         <v>5</v>
@@ -1824,7 +1845,7 @@
         <v>19.716999999999643</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="3" t="s">
         <v>6</v>
@@ -1844,7 +1865,7 @@
         <v>90.423999999999978</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>1953</v>
       </c>
@@ -1866,7 +1887,7 @@
         <v>52.870000000000346</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="3" t="s">
         <v>4</v>
@@ -1886,7 +1907,7 @@
         <v>22.394999999999982</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="3" t="s">
         <v>5</v>
@@ -1906,7 +1927,7 @@
         <v>-16.421000000000276</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
         <v>6</v>
@@ -1926,7 +1947,7 @@
         <v>-43.940000000000055</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>1954</v>
       </c>
@@ -1948,7 +1969,7 @@
         <v>-13.652999999999793</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="3" t="s">
         <v>4</v>
@@ -1968,7 +1989,7 @@
         <v>3.112999999999829</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="3" t="s">
         <v>5</v>
@@ -1988,7 +2009,7 @@
         <v>32.177000000000135</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="3" t="s">
         <v>6</v>
@@ -2008,7 +2029,7 @@
         <v>56.369999999999891</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>1955</v>
       </c>
@@ -2030,7 +2051,7 @@
         <v>83.894000000000233</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="3" t="s">
         <v>4</v>
@@ -2050,7 +2071,7 @@
         <v>49.16399999999976</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="3" t="s">
         <v>5</v>
@@ -2070,7 +2091,7 @@
         <v>41.469000000000051</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="3" t="s">
         <v>6</v>
@@ -2090,7 +2111,7 @@
         <v>18.689000000000306</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>1956</v>
       </c>
@@ -2112,7 +2133,7 @@
         <v>-12.146000000000186</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="3" t="s">
         <v>4</v>
@@ -2132,7 +2153,7 @@
         <v>25.771999999999935</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="3" t="s">
         <v>5</v>
@@ -2152,7 +2173,7 @@
         <v>-2.8200000000001637</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="3" t="s">
         <v>6</v>
@@ -2172,7 +2193,7 @@
         <v>51.696000000000367</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>1957</v>
       </c>
@@ -2194,7 +2215,7 @@
         <v>20.440999999999804</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="3" t="s">
         <v>4</v>
@@ -2214,7 +2235,7 @@
         <v>-7.0410000000001673</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="3" t="s">
         <v>5</v>
@@ -2234,7 +2255,7 @@
         <v>31.416000000000167</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" s="3" t="s">
         <v>6</v>
@@ -2254,7 +2275,7 @@
         <v>-33.492000000000189</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>1958</v>
       </c>
@@ -2276,7 +2297,7 @@
         <v>-83.169999999999618</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="3" t="s">
         <v>4</v>
@@ -2296,7 +2317,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="3" t="s">
         <v>5</v>
@@ -2316,7 +2337,7 @@
         <v>72.659999999999854</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="3" t="s">
         <v>6</v>
@@ -2336,7 +2357,7 @@
         <v>75.148000000000138</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>1959</v>
       </c>
@@ -2358,7 +2379,7 @@
         <v>63.096999999999753</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="3" t="s">
         <v>4</v>
@@ -2378,7 +2399,7 @@
         <v>75.538000000000011</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="3" t="s">
         <v>5</v>
@@ -2398,7 +2419,7 @@
         <v>2.3899999999998727</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="3" t="s">
         <v>6</v>
@@ -2418,7 +2439,7 @@
         <v>9.7750000000000909</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>1960</v>
       </c>
@@ -2440,7 +2461,7 @@
         <v>77.34900000000016</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="3" t="s">
         <v>4</v>
@@ -2460,7 +2481,7 @@
         <v>-18.934999999999945</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="3" t="s">
         <v>5</v>
@@ -2480,7 +2501,7 @@
         <v>17.139000000000124</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="B57" s="3" t="s">
         <v>6</v>
@@ -2500,7 +2521,7 @@
         <v>-45.107000000000426</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>1961</v>
       </c>
@@ -2522,7 +2543,7 @@
         <v>23.425000000000182</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
       <c r="B59" s="3" t="s">
         <v>4</v>
@@ -2542,7 +2563,7 @@
         <v>59.318000000000211</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="3" t="s">
         <v>5</v>
@@ -2562,7 +2583,7 @@
         <v>68.230999999999767</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="3" t="s">
         <v>6</v>
@@ -2582,7 +2603,7 @@
         <v>71.037000000000262</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>1962</v>
       </c>
@@ -2604,7 +2625,7 @@
         <v>65.85799999999972</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="B63" s="3" t="s">
         <v>4</v>
@@ -2624,7 +2645,7 @@
         <v>34.001999999999953</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="B64" s="3" t="s">
         <v>5</v>
@@ -2644,7 +2665,7 @@
         <v>46.626999999999953</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="B65" s="3" t="s">
         <v>6</v>
@@ -2664,7 +2685,7 @@
         <v>12.644999999999982</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>1963</v>
       </c>
@@ -2686,7 +2707,7 @@
         <v>42.061000000000149</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="3" t="s">
         <v>4</v>
@@ -2706,7 +2727,7 @@
         <v>43.701000000000022</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" s="3" t="s">
         <v>5</v>
@@ -2726,7 +2747,7 @@
         <v>86.572000000000116</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
       <c r="B69" s="3" t="s">
         <v>6</v>
@@ -2746,7 +2767,7 @@
         <v>26.391999999999825</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>1964</v>
       </c>
@@ -2768,7 +2789,7 @@
         <v>85.405999999999949</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" s="3" t="s">
         <v>4</v>
@@ -2788,7 +2809,7 @@
         <v>45.03899999999976</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" s="3" t="s">
         <v>5</v>
@@ -2808,7 +2829,7 @@
         <v>65.326000000000022</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" s="3" t="s">
         <v>6</v>
@@ -2828,7 +2849,7 @@
         <v>13.128000000000611</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>1965</v>
       </c>
@@ -2850,7 +2871,7 @@
         <v>103.0649999999996</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" s="3" t="s">
         <v>4</v>
@@ -2870,7 +2891,7 @@
         <v>55.114000000000487</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
       <c r="B76" s="3" t="s">
         <v>5</v>
@@ -2890,7 +2911,7 @@
         <v>98.201999999999316</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="B77" s="3" t="s">
         <v>6</v>
@@ -2910,7 +2931,7 @@
         <v>104.03099999999995</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>1966</v>
       </c>
@@ -2932,7 +2953,7 @@
         <v>112.43000000000029</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="3" t="s">
         <v>4</v>
@@ -2952,7 +2973,7 @@
         <v>16.158000000000357</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" s="3" t="s">
         <v>5</v>
@@ -2972,7 +2993,7 @@
         <v>40.207999999999629</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
       <c r="B81" s="3" t="s">
         <v>6</v>
@@ -2992,7 +3013,7 @@
         <v>39.283000000000357</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>1967</v>
       </c>
@@ -3014,7 +3035,7 @@
         <v>42.761999999999716</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="3" t="s">
         <v>4</v>
@@ -3034,7 +3055,7 @@
         <v>2.9880000000002838</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
       <c r="B84" s="3" t="s">
         <v>5</v>
@@ -3054,7 +3075,7 @@
         <v>46.104999999999563</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
       <c r="B85" s="3" t="s">
         <v>6</v>
@@ -3074,7 +3095,7 @@
         <v>37.085000000000036</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>1968</v>
       </c>
@@ -3096,7 +3117,7 @@
         <v>101.07600000000002</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
       <c r="B87" s="3" t="s">
         <v>4</v>
@@ -3116,7 +3137,7 @@
         <v>84.480000000000473</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
       <c r="B88" s="3" t="s">
         <v>5</v>
@@ -3136,7 +3157,7 @@
         <v>39.826000000000022</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
       <c r="B89" s="3" t="s">
         <v>6</v>
@@ -3156,7 +3177,7 @@
         <v>20.353000000000065</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>1969</v>
       </c>
@@ -3178,7 +3199,7 @@
         <v>81.384999999999309</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
       <c r="B91" s="3" t="s">
         <v>4</v>
@@ -3198,7 +3219,7 @@
         <v>16.028000000000247</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="3" t="s">
         <v>5</v>
@@ -3218,7 +3239,7 @@
         <v>34.975000000000364</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="3" t="s">
         <v>6</v>
@@ -3238,7 +3259,7 @@
         <v>-26.044000000000779</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>1970</v>
       </c>
@@ -3260,7 +3281,7 @@
         <v>-7.9039999999995416</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
       <c r="B95" s="3" t="s">
         <v>4</v>
@@ -3280,7 +3301,7 @@
         <v>7.5119999999997162</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="3" t="s">
         <v>5</v>
@@ -3300,7 +3321,7 @@
         <v>48.913000000000466</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
       <c r="B97" s="3" t="s">
         <v>6</v>
@@ -3320,7 +3341,7 @@
         <v>-57.405000000000655</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>1971</v>
       </c>
@@ -3342,7 +3363,7 @@
         <v>143.94700000000012</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
       <c r="B99" s="3" t="s">
         <v>4</v>
@@ -3362,7 +3383,7 @@
         <v>29.440000000000509</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
       <c r="B100" s="3" t="s">
         <v>5</v>
@@ -3382,7 +3403,7 @@
         <v>45.01299999999992</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
       <c r="B101" s="3" t="s">
         <v>6</v>
@@ -3402,7 +3423,7 @@
         <v>12.960000000000036</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>1972</v>
       </c>
@@ -3424,7 +3445,7 @@
         <v>101.61700000000019</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
       <c r="B103" s="3" t="s">
         <v>4</v>
@@ -3444,7 +3465,7 @@
         <v>127.82099999999991</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
       <c r="B104" s="3" t="s">
         <v>5</v>
@@ -3464,7 +3485,7 @@
         <v>54.384000000000015</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
       <c r="B105" s="3" t="s">
         <v>6</v>
@@ -3484,7 +3505,7 @@
         <v>97.365999999999985</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>1973</v>
       </c>
@@ -3506,7 +3527,7 @@
         <v>146.32399999999961</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
       <c r="B107" s="3" t="s">
         <v>4</v>
@@ -3526,7 +3547,7 @@
         <v>65.962000000000444</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
       <c r="B108" s="3" t="s">
         <v>5</v>
@@ -3546,7 +3567,7 @@
         <v>-32.204999999999927</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
       <c r="B109" s="3" t="s">
         <v>6</v>
@@ -3566,7 +3587,7 @@
         <v>57.829999999999927</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>1974</v>
       </c>
@@ -3588,7 +3609,7 @@
         <v>-52.873000000000502</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
       <c r="B111" s="3" t="s">
         <v>4</v>
@@ -3608,7 +3629,7 @@
         <v>14.493000000000393</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
       <c r="B112" s="3" t="s">
         <v>5</v>
@@ -3628,7 +3649,7 @@
         <v>-57.773000000000138</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
       <c r="B113" s="3" t="s">
         <v>6</v>
@@ -3648,7 +3669,7 @@
         <v>-23.514000000000124</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>1975</v>
       </c>
@@ -3670,7 +3691,7 @@
         <v>-73.429000000000087</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
       <c r="B115" s="3" t="s">
         <v>4</v>
@@ -3690,7 +3711,7 @@
         <v>42.574999999999818</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
       <c r="B116" s="3" t="s">
         <v>5</v>
@@ -3710,7 +3731,7 @@
         <v>102.71600000000035</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
       <c r="B117" s="3" t="s">
         <v>6</v>
@@ -3730,7 +3751,7 @@
         <v>82.203999999999724</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>1976</v>
       </c>
@@ -3752,7 +3773,7 @@
         <v>139.1190000000006</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
       <c r="B119" s="3" t="s">
         <v>4</v>
@@ -3772,7 +3793,7 @@
         <v>46.375999999999294</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
       <c r="B120" s="3" t="s">
         <v>5</v>
@@ -3792,7 +3813,7 @@
         <v>34.8700000000008</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
       <c r="B121" s="3" t="s">
         <v>6</v>
@@ -3812,7 +3833,7 @@
         <v>46.281999999999243</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>1977</v>
       </c>
@@ -3834,7 +3855,7 @@
         <v>76.526000000000749</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
       <c r="B123" s="3" t="s">
         <v>4</v>
@@ -3854,7 +3875,7 @@
         <v>126.76299999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
       <c r="B124" s="3" t="s">
         <v>5</v>
@@ -3874,7 +3895,7 @@
         <v>119.99099999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
       <c r="B125" s="3" t="s">
         <v>6</v>
@@ -3894,7 +3915,7 @@
         <v>0.13499999999930878</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>1978</v>
       </c>
@@ -3916,7 +3937,7 @@
         <v>21.668000000000575</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
       <c r="B127" s="3" t="s">
         <v>4</v>
@@ -3936,7 +3957,7 @@
         <v>262.65999999999985</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
       <c r="B128" s="3" t="s">
         <v>5</v>
@@ -3956,7 +3977,7 @@
         <v>70.994999999999891</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
       <c r="B129" s="3" t="s">
         <v>6</v>
@@ -3976,7 +3997,7 @@
         <v>95.835000000000036</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>1979</v>
       </c>
@@ -3998,7 +4019,7 @@
         <v>12.976999999999862</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
       <c r="B131" s="3" t="s">
         <v>4</v>
@@ -4018,7 +4039,7 @@
         <v>7.7269999999998618</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
       <c r="B132" s="3" t="s">
         <v>5</v>
@@ -4038,7 +4059,7 @@
         <v>53.827000000000226</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
       <c r="B133" s="3" t="s">
         <v>6</v>
@@ -4058,7 +4079,7 @@
         <v>18.253999999999905</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>1980</v>
       </c>
@@ -4080,7 +4101,7 @@
         <v>23.021999999999935</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
       <c r="B135" s="3" t="s">
         <v>4</v>
@@ -4100,7 +4121,7 @@
         <v>-151.26800000000003</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
       <c r="B136" s="3" t="s">
         <v>5</v>
@@ -4120,7 +4141,7 @@
         <v>-8.545999999999367</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
       <c r="B137" s="3" t="s">
         <v>6</v>
@@ -4140,7 +4161,7 @@
         <v>133.93399999999929</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>1981</v>
       </c>
@@ -4162,7 +4183,7 @@
         <v>143.34500000000025</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
       <c r="B139" s="3" t="s">
         <v>4</v>
@@ -4182,7 +4203,7 @@
         <v>-55.277000000000044</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
       <c r="B140" s="3" t="s">
         <v>5</v>
@@ -4202,7 +4223,7 @@
         <v>88.659999999999854</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
       <c r="B141" s="3" t="s">
         <v>6</v>
@@ -4222,7 +4243,7 @@
         <v>-81.636999999999716</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>1982</v>
       </c>
@@ -4244,7 +4265,7 @@
         <v>-115.13699999999972</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
       <c r="B143" s="3" t="s">
         <v>4</v>
@@ -4264,7 +4285,7 @@
         <v>33.280999999999949</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
       <c r="B144" s="3" t="s">
         <v>5</v>
@@ -4284,7 +4305,7 @@
         <v>-28.016000000000531</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
       <c r="B145" s="3" t="s">
         <v>6</v>
@@ -4304,7 +4325,7 @@
         <v>2.9210000000002765</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>1983</v>
       </c>
@@ -4326,7 +4347,7 @@
         <v>96.248999999999796</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
       <c r="B147" s="3" t="s">
         <v>4</v>
@@ -4346,7 +4367,7 @@
         <v>168.39000000000033</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
       <c r="B148" s="3" t="s">
         <v>5</v>
@@ -4366,7 +4387,7 @@
         <v>151.28999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
       <c r="B149" s="3" t="s">
         <v>6</v>
@@ -4386,7 +4407,7 @@
         <v>161.04799999999977</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>1984</v>
       </c>
@@ -4408,7 +4429,7 @@
         <v>154.05299999999988</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
       <c r="B151" s="3" t="s">
         <v>4</v>
@@ -4428,7 +4449,7 @@
         <v>138.82300000000032</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
       <c r="B152" s="3" t="s">
         <v>5</v>
@@ -4448,7 +4469,7 @@
         <v>78.795000000000073</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
       <c r="B153" s="3" t="s">
         <v>6</v>
@@ -4468,7 +4489,7 @@
         <v>67.734000000000378</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>1985</v>
       </c>
@@ -4490,7 +4511,7 @@
         <v>80.620999999999185</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
       <c r="B155" s="3" t="s">
         <v>4</v>
@@ -4510,7 +4531,7 @@
         <v>73.967000000000553</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
       <c r="B156" s="3" t="s">
         <v>5</v>
@@ -4530,7 +4551,7 @@
         <v>129.43299999999908</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
       <c r="B157" s="3" t="s">
         <v>6</v>
@@ -4550,7 +4571,7 @@
         <v>63.968000000000757</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>1986</v>
       </c>
@@ -4572,7 +4593,7 @@
         <v>80.939000000000306</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
       <c r="B159" s="3" t="s">
         <v>4</v>
@@ -4592,7 +4613,7 @@
         <v>39.396999999999025</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
       <c r="B160" s="3" t="s">
         <v>5</v>
@@ -4612,7 +4633,7 @@
         <v>84.077000000001135</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
       <c r="B161" s="3" t="s">
         <v>6</v>
@@ -4632,7 +4653,7 @@
         <v>47.591999999998734</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>1987</v>
       </c>
@@ -4654,7 +4675,7 @@
         <v>66.174000000000888</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
       <c r="B163" s="3" t="s">
         <v>4</v>
@@ -4674,7 +4695,7 @@
         <v>96.888999999999214</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
       <c r="B164" s="3" t="s">
         <v>5</v>
@@ -4694,7 +4715,7 @@
         <v>78.768000000000029</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
       <c r="B165" s="3" t="s">
         <v>6</v>
@@ -4714,7 +4735,7 @@
         <v>157.3080000000009</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>1988</v>
       </c>
@@ -4736,7 +4757,7 @@
         <v>48.170000000000073</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
       <c r="B167" s="3" t="s">
         <v>4</v>
@@ -4756,7 +4777,7 @@
         <v>123.09199999999873</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
       <c r="B168" s="3" t="s">
         <v>5</v>
@@ -4776,7 +4797,7 @@
         <v>55.61200000000099</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
       <c r="B169" s="3" t="s">
         <v>6</v>
@@ -4796,7 +4817,7 @@
         <v>127.19900000000052</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>1989</v>
       </c>
@@ -4818,7 +4839,7 @@
         <v>98.319999999999709</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
       <c r="B171" s="3" t="s">
         <v>4</v>
@@ -4838,7 +4859,7 @@
         <v>74.567999999999302</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
       <c r="B172" s="3" t="s">
         <v>5</v>
@@ -4858,7 +4879,7 @@
         <v>72.934999999999491</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
       <c r="B173" s="3" t="s">
         <v>6</v>
@@ -4878,7 +4899,7 @@
         <v>19.539000000000669</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>1990</v>
       </c>
@@ -4900,7 +4921,7 @@
         <v>108.6190000000006</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
       <c r="B175" s="3" t="s">
         <v>4</v>
@@ -4920,7 +4941,7 @@
         <v>36.468999999999141</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
       <c r="B176" s="3" t="s">
         <v>5</v>
@@ -4940,7 +4961,7 @@
         <v>6.7139999999999418</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
       <c r="B177" s="3" t="s">
         <v>6</v>
@@ -4960,7 +4981,7 @@
         <v>-91.864999999999782</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>1991</v>
       </c>
@@ -4982,7 +5003,7 @@
         <v>-46.788000000000466</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
       <c r="B179" s="3" t="s">
         <v>4</v>
@@ -5002,7 +5023,7 @@
         <v>77.59400000000096</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
       <c r="B180" s="3" t="s">
         <v>5</v>
@@ -5022,7 +5043,7 @@
         <v>50.684999999999491</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
       <c r="B181" s="3" t="s">
         <v>6</v>
@@ -5042,7 +5063,7 @@
         <v>35.134000000000015</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>1992</v>
       </c>
@@ -5064,7 +5085,7 @@
         <v>121.10599999999977</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
       <c r="B183" s="3" t="s">
         <v>4</v>
@@ -5084,7 +5105,7 @@
         <v>110.9940000000006</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
       <c r="B184" s="3" t="s">
         <v>5</v>
@@ -5104,7 +5125,7 @@
         <v>102.2440000000006</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
       <c r="B185" s="3" t="s">
         <v>6</v>
@@ -5124,7 +5145,7 @@
         <v>108.97499999999854</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>1993</v>
       </c>
@@ -5146,7 +5167,7 @@
         <v>17.627000000000407</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
       <c r="B187" s="3" t="s">
         <v>4</v>
@@ -5166,7 +5187,7 @@
         <v>61.572000000000116</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
       <c r="B188" s="3" t="s">
         <v>5</v>
@@ -5186,7 +5207,7 @@
         <v>50.759000000000015</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
       <c r="B189" s="3" t="s">
         <v>6</v>
@@ -5206,7 +5227,7 @@
         <v>145.3809999999994</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>1994</v>
       </c>
@@ -5228,7 +5249,7 @@
         <v>105.12900000000081</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
       <c r="B191" s="3" t="s">
         <v>4</v>
@@ -5248,7 +5269,7 @@
         <v>148.2450000000008</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
       <c r="B192" s="3" t="s">
         <v>5</v>
@@ -5268,7 +5289,7 @@
         <v>64.81499999999869</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
       <c r="B193" s="3" t="s">
         <v>6</v>
@@ -5288,7 +5309,7 @@
         <v>127.75600000000122</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>1995</v>
       </c>
@@ -5310,7 +5331,7 @@
         <v>40.018999999998414</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
       <c r="B195" s="3" t="s">
         <v>4</v>
@@ -5330,7 +5351,7 @@
         <v>33.770000000000437</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
       <c r="B196" s="3" t="s">
         <v>5</v>
@@ -5350,7 +5371,7 @@
         <v>96.588999999999942</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
       <c r="B197" s="3" t="s">
         <v>6</v>
@@ -5370,7 +5391,7 @@
         <v>77.756999999999607</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>1996</v>
       </c>
@@ -5392,7 +5413,7 @@
         <v>86.351000000000568</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
       <c r="B199" s="3" t="s">
         <v>4</v>
@@ -5412,7 +5433,7 @@
         <v>193.72199999999975</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
       <c r="B200" s="3" t="s">
         <v>5</v>
@@ -5432,7 +5453,7 @@
         <v>105.92300000000068</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
       <c r="B201" s="3" t="s">
         <v>6</v>
@@ -5452,7 +5473,7 @@
         <v>123.71199999999953</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>1997</v>
       </c>
@@ -5474,7 +5495,7 @@
         <v>77.697000000000116</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="5"/>
       <c r="B203" s="3" t="s">
         <v>4</v>
@@ -5494,7 +5515,7 @@
         <v>201.7489999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="5"/>
       <c r="B204" s="3" t="s">
         <v>5</v>
@@ -5514,7 +5535,7 @@
         <v>153.78900000000067</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="5"/>
       <c r="B205" s="3" t="s">
         <v>6</v>
@@ -5534,7 +5555,7 @@
         <v>106.48500000000058</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>1998</v>
       </c>
@@ -5556,7 +5577,7 @@
         <v>126.24699999999939</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="5"/>
       <c r="B207" s="3" t="s">
         <v>4</v>
@@ -5576,7 +5597,7 @@
         <v>117.59699999999975</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="5"/>
       <c r="B208" s="3" t="s">
         <v>5</v>
@@ -5596,7 +5617,7 @@
         <v>161.41300000000047</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="5"/>
       <c r="B209" s="3" t="s">
         <v>6</v>
@@ -5616,7 +5637,7 @@
         <v>208.91799999999967</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>1999</v>
       </c>
@@ -5638,7 +5659,7 @@
         <v>123.92699999999968</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="5"/>
       <c r="B211" s="3" t="s">
         <v>4</v>
@@ -5658,7 +5679,7 @@
         <v>111.15099999999984</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="5"/>
       <c r="B212" s="3" t="s">
         <v>5</v>
@@ -5678,7 +5699,7 @@
         <v>178.02300000000105</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="5"/>
       <c r="B213" s="3" t="s">
         <v>6</v>
@@ -5698,7 +5719,7 @@
         <v>223.20899999999892</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>2000</v>
       </c>
@@ -5720,7 +5741,7 @@
         <v>50.167000000001281</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="5"/>
       <c r="B215" s="3" t="s">
         <v>4</v>
@@ -5740,7 +5761,7 @@
         <v>252.7609999999986</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="5"/>
       <c r="B216" s="3" t="s">
         <v>5</v>
@@ -5760,7 +5781,7 @@
         <v>14.404000000000451</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="5"/>
       <c r="B217" s="3" t="s">
         <v>6</v>
@@ -5780,7 +5801,7 @@
         <v>84.45299999999952</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>2001</v>
       </c>
@@ -5802,7 +5823,7 @@
         <v>-46.644999999998618</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="5"/>
       <c r="B219" s="3" t="s">
         <v>4</v>
@@ -5822,7 +5843,7 @@
         <v>88.573999999998705</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="5"/>
       <c r="B220" s="3" t="s">
         <v>5</v>
@@ -5842,7 +5863,7 @@
         <v>-57.177999999999884</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="5"/>
       <c r="B221" s="3" t="s">
         <v>6</v>
@@ -5862,7 +5883,7 @@
         <v>39.058000000000902</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>2002</v>
       </c>
@@ -5884,7 +5905,7 @@
         <v>119.21099999999933</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="5"/>
       <c r="B223" s="3" t="s">
         <v>4</v>
@@ -5904,7 +5925,7 @@
         <v>88.063000000000102</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="5"/>
       <c r="B224" s="3" t="s">
         <v>5</v>
@@ -5924,7 +5945,7 @@
         <v>58.784999999999854</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="5"/>
       <c r="B225" s="3" t="s">
         <v>6</v>
@@ -5944,7 +5965,7 @@
         <v>17.947000000000116</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>2003</v>
       </c>
@@ -5966,7 +5987,7 @@
         <v>76.560999999999694</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="5"/>
       <c r="B227" s="3" t="s">
         <v>4</v>
@@ -5986,7 +6007,7 @@
         <v>129.42599999999948</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="5"/>
       <c r="B228" s="3" t="s">
         <v>5</v>
@@ -6006,7 +6027,7 @@
         <v>245.21500000000015</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="5"/>
       <c r="B229" s="3" t="s">
         <v>6</v>
@@ -6026,7 +6047,7 @@
         <v>173.97800000000097</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>2004</v>
       </c>
@@ -6048,7 +6069,7 @@
         <v>85.920000000000073</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="5"/>
       <c r="B231" s="3" t="s">
         <v>4</v>
@@ -6068,7 +6089,7 @@
         <v>118.17000000000007</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="5"/>
       <c r="B232" s="3" t="s">
         <v>5</v>
@@ -6088,7 +6109,7 @@
         <v>145.76900000000023</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="5"/>
       <c r="B233" s="3" t="s">
         <v>6</v>
@@ -6108,7 +6129,7 @@
         <v>158.2609999999986</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>2005</v>
       </c>
@@ -6130,7 +6151,7 @@
         <v>173.84700000000157</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="5"/>
       <c r="B235" s="3" t="s">
         <v>4</v>
@@ -6150,7 +6171,7 @@
         <v>78.054999999998472</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="5"/>
       <c r="B236" s="3" t="s">
         <v>5</v>
@@ -6170,7 +6191,7 @@
         <v>124.80500000000029</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="5"/>
       <c r="B237" s="3" t="s">
         <v>6</v>
@@ -6190,7 +6211,7 @@
         <v>89.147000000000844</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>2006</v>
       </c>
@@ -6212,7 +6233,7 @@
         <v>217.10099999999875</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="5"/>
       <c r="B239" s="3" t="s">
         <v>4</v>
@@ -6232,7 +6253,7 @@
         <v>42.316000000002532</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="5"/>
       <c r="B240" s="3" t="s">
         <v>5</v>
@@ -6252,7 +6273,7 @@
         <v>24.586999999999534</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="5"/>
       <c r="B241" s="3" t="s">
         <v>6</v>
@@ -6272,7 +6293,7 @@
         <v>141.12800000000061</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>2007</v>
       </c>
@@ -6294,7 +6315,7 @@
         <v>49.823999999996886</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="5"/>
       <c r="B243" s="3" t="s">
         <v>4</v>
@@ -6314,7 +6335,7 @@
         <v>101.6239999999998</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="5"/>
       <c r="B244" s="3" t="s">
         <v>5</v>
@@ -6334,7 +6355,7 @@
         <v>96.273000000001048</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="5"/>
       <c r="B245" s="3" t="s">
         <v>6</v>
@@ -6354,7 +6375,7 @@
         <v>105.60399999999936</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>2008</v>
       </c>
@@ -6376,7 +6397,7 @@
         <v>-72.187999999998283</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="5"/>
       <c r="B247" s="3" t="s">
         <v>4</v>
@@ -6396,7 +6417,7 @@
         <v>100.28800000000047</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="5"/>
       <c r="B248" s="3" t="s">
         <v>5</v>
@@ -6416,7 +6437,7 @@
         <v>-88.996000000002823</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="5"/>
       <c r="B249" s="3" t="s">
         <v>6</v>
@@ -6436,7 +6457,7 @@
         <v>-368.94499999999971</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>2009</v>
       </c>
@@ -6458,7 +6479,7 @@
         <v>-187.08799999999792</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="5"/>
       <c r="B251" s="3" t="s">
         <v>4</v>
@@ -6478,7 +6499,7 @@
         <v>-29.117000000000189</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="5"/>
       <c r="B252" s="3" t="s">
         <v>5</v>
@@ -6498,7 +6519,7 @@
         <v>57.136000000000422</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="5"/>
       <c r="B253" s="3" t="s">
         <v>6</v>
@@ -6518,7 +6539,7 @@
         <v>176.47299999999996</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>2010</v>
       </c>
@@ -6540,7 +6561,7 @@
         <v>79.955999999998312</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="5"/>
       <c r="B255" s="3" t="s">
         <v>4</v>
@@ -6560,7 +6581,7 @@
         <v>160.45200000000114</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="5"/>
       <c r="B256" s="3" t="s">
         <v>5</v>
@@ -6580,7 +6601,7 @@
         <v>129.10399999999936</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="5"/>
       <c r="B257" s="3" t="s">
         <v>6</v>
@@ -6600,7 +6621,7 @@
         <v>88.598000000001775</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>2011</v>
       </c>
@@ -6622,7 +6643,7 @@
         <v>-40.231999999999971</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="5"/>
       <c r="B259" s="3" t="s">
         <v>4</v>
@@ -6642,7 +6663,7 @@
         <v>114.48199999999997</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="5"/>
       <c r="B260" s="3" t="s">
         <v>5</v>
@@ -6651,18 +6672,18 @@
         <v>17031.312999999998</v>
       </c>
       <c r="D260" s="4">
-        <f t="shared" ref="D260:D309" si="8">C259</f>
+        <f t="shared" ref="D260:D318" si="8">C259</f>
         <v>17035.114000000001</v>
       </c>
       <c r="E260">
         <v>258</v>
       </c>
       <c r="F260" s="4">
-        <f t="shared" ref="F260:F309" si="9">C260-D260</f>
+        <f t="shared" ref="F260:F318" si="9">C260-D260</f>
         <v>-3.8010000000031141</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="5"/>
       <c r="B261" s="3" t="s">
         <v>6</v>
@@ -6682,7 +6703,7 @@
         <v>191.27000000000044</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>2012</v>
       </c>
@@ -6704,7 +6725,7 @@
         <v>144.42699999999968</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="5"/>
       <c r="B263" s="3" t="s">
         <v>4</v>
@@ -6724,7 +6745,7 @@
         <v>77.515000000003056</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="5"/>
       <c r="B264" s="3" t="s">
         <v>5</v>
@@ -6744,7 +6765,7 @@
         <v>25.125</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="5"/>
       <c r="B265" s="3" t="s">
         <v>6</v>
@@ -6764,7 +6785,7 @@
         <v>20.201999999997497</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>2013</v>
       </c>
@@ -6786,7 +6807,7 @@
         <v>172.5480000000025</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="5"/>
       <c r="B267" s="3" t="s">
         <v>4</v>
@@ -6806,7 +6827,7 @@
         <v>47.270999999997002</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="5"/>
       <c r="B268" s="3" t="s">
         <v>5</v>
@@ -6826,7 +6847,7 @@
         <v>150.77900000000227</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="5"/>
       <c r="B269" s="3" t="s">
         <v>6</v>
@@ -6846,7 +6867,7 @@
         <v>155.69700000000012</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>2014</v>
       </c>
@@ -6868,7 +6889,7 @@
         <v>-62.173000000002503</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="5"/>
       <c r="B271" s="3" t="s">
         <v>4</v>
@@ -6888,7 +6909,7 @@
         <v>231.93700000000172</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="5"/>
       <c r="B272" s="3" t="s">
         <v>5</v>
@@ -6908,7 +6929,7 @@
         <v>221.02999999999884</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="5"/>
       <c r="B273" s="3" t="s">
         <v>6</v>
@@ -6928,7 +6949,7 @@
         <v>93.090000000000146</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>2015</v>
       </c>
@@ -6950,7 +6971,7 @@
         <v>166.59000000000015</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="5"/>
       <c r="B275" s="3" t="s">
         <v>4</v>
@@ -6970,7 +6991,7 @@
         <v>115.62199999999939</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="5"/>
       <c r="B276" s="3" t="s">
         <v>5</v>
@@ -6990,7 +7011,7 @@
         <v>75.17500000000291</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="5"/>
       <c r="B277" s="3" t="s">
         <v>6</v>
@@ -7010,7 +7031,7 @@
         <v>34.787999999996828</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>2016</v>
       </c>
@@ -7032,7 +7053,7 @@
         <v>109.48400000000038</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="5"/>
       <c r="B279" s="3" t="s">
         <v>4</v>
@@ -7052,7 +7073,7 @@
         <v>61.019000000000233</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="5"/>
       <c r="B280" s="3" t="s">
         <v>5</v>
@@ -7072,7 +7093,7 @@
         <v>135.22899999999936</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="5"/>
       <c r="B281" s="3" t="s">
         <v>6</v>
@@ -7092,7 +7113,7 @@
         <v>106.41400000000067</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>2017</v>
       </c>
@@ -7114,7 +7135,7 @@
         <v>93.991000000001804</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="5"/>
       <c r="B283" s="3" t="s">
         <v>4</v>
@@ -7134,7 +7155,7 @@
         <v>108.60599999999977</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="5"/>
       <c r="B284" s="3" t="s">
         <v>5</v>
@@ -7154,7 +7175,7 @@
         <v>153.8169999999991</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="5"/>
       <c r="B285" s="3" t="s">
         <v>6</v>
@@ -7174,7 +7195,7 @@
         <v>221.58599999999933</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>2018</v>
       </c>
@@ -7196,7 +7217,7 @@
         <v>161.72500000000218</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="5"/>
       <c r="B287" s="3" t="s">
         <v>4</v>
@@ -7216,7 +7237,7 @@
         <v>106.39899999999761</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="5"/>
       <c r="B288" s="3" t="s">
         <v>5</v>
@@ -7236,7 +7257,7 @@
         <v>125.67799999999988</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="5"/>
       <c r="B289" s="3" t="s">
         <v>6</v>
@@ -7256,7 +7277,7 @@
         <v>28.720000000001164</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>2019</v>
       </c>
@@ -7264,7 +7285,7 @@
         <v>3</v>
       </c>
       <c r="C290" s="4">
-        <v>20415.150000000001</v>
+        <v>20431.599999999999</v>
       </c>
       <c r="D290" s="4">
         <f t="shared" si="8"/>
@@ -7275,70 +7296,70 @@
       </c>
       <c r="F290" s="4">
         <f t="shared" si="9"/>
-        <v>110.27600000000166</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+        <v>126.72599999999875</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="5"/>
       <c r="B291" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C291" s="4">
-        <v>20584.527999999998</v>
+        <v>20602.3</v>
       </c>
       <c r="D291" s="4">
         <f t="shared" si="8"/>
-        <v>20415.150000000001</v>
+        <v>20431.599999999999</v>
       </c>
       <c r="E291">
         <v>289</v>
       </c>
       <c r="F291" s="4">
         <f t="shared" si="9"/>
-        <v>169.37799999999697</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+        <v>170.70000000000073</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="5"/>
       <c r="B292" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C292" s="4">
-        <v>20817.580999999998</v>
+        <v>20843.3</v>
       </c>
       <c r="D292" s="4">
         <f t="shared" si="8"/>
-        <v>20584.527999999998</v>
+        <v>20602.3</v>
       </c>
       <c r="E292">
         <v>290</v>
       </c>
       <c r="F292" s="4">
         <f t="shared" si="9"/>
-        <v>233.05299999999988</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="5"/>
       <c r="B293" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C293" s="4">
-        <v>20951.088</v>
+        <v>20985.4</v>
       </c>
       <c r="D293" s="4">
         <f t="shared" si="8"/>
-        <v>20817.580999999998</v>
+        <v>20843.3</v>
       </c>
       <c r="E293">
         <v>291</v>
       </c>
       <c r="F293" s="4">
         <f t="shared" si="9"/>
-        <v>133.50700000000143</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+        <v>142.10000000000218</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>2020</v>
       </c>
@@ -7346,81 +7367,81 @@
         <v>3</v>
       </c>
       <c r="C294" s="4">
-        <v>20665.553</v>
+        <v>20709.2</v>
       </c>
       <c r="D294" s="4">
         <f t="shared" si="8"/>
-        <v>20951.088</v>
+        <v>20985.4</v>
       </c>
       <c r="E294">
         <v>292</v>
       </c>
       <c r="F294" s="4">
         <f t="shared" si="9"/>
-        <v>-285.53499999999985</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-276.20000000000073</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="5"/>
       <c r="B295" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C295" s="4">
-        <v>19034.830000000002</v>
+        <v>19078</v>
       </c>
       <c r="D295" s="4">
         <f t="shared" si="8"/>
-        <v>20665.553</v>
+        <v>20709.2</v>
       </c>
       <c r="E295">
         <v>293</v>
       </c>
       <c r="F295" s="4">
         <f t="shared" si="9"/>
-        <v>-1630.7229999999981</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-1631.2000000000007</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="5"/>
       <c r="B296" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C296" s="4">
-        <v>20511.785</v>
+        <v>20558.900000000001</v>
       </c>
       <c r="D296" s="4">
         <f t="shared" si="8"/>
-        <v>19034.830000000002</v>
+        <v>19078</v>
       </c>
       <c r="E296">
         <v>294</v>
       </c>
       <c r="F296" s="4">
         <f t="shared" si="9"/>
-        <v>1476.9549999999981</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1480.9000000000015</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="5"/>
       <c r="B297" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C297" s="4">
-        <v>20724.128000000001</v>
+        <v>20791.900000000001</v>
       </c>
       <c r="D297" s="4">
         <f t="shared" si="8"/>
-        <v>20511.785</v>
+        <v>20558.900000000001</v>
       </c>
       <c r="E297">
         <v>295</v>
       </c>
       <c r="F297" s="4">
         <f t="shared" si="9"/>
-        <v>212.34300000000076</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>2021</v>
       </c>
@@ -7428,81 +7449,81 @@
         <v>3</v>
       </c>
       <c r="C298" s="4">
-        <v>20990.541000000001</v>
+        <v>21082.1</v>
       </c>
       <c r="D298" s="4">
         <f t="shared" si="8"/>
-        <v>20724.128000000001</v>
+        <v>20791.900000000001</v>
       </c>
       <c r="E298">
         <v>296</v>
       </c>
       <c r="F298" s="4">
         <f t="shared" si="9"/>
-        <v>266.41300000000047</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+        <v>290.19999999999709</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="5"/>
       <c r="B299" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C299" s="4">
-        <v>21309.544000000002</v>
+        <v>21440.9</v>
       </c>
       <c r="D299" s="4">
         <f t="shared" si="8"/>
-        <v>20990.541000000001</v>
+        <v>21082.1</v>
       </c>
       <c r="E299">
         <v>297</v>
       </c>
       <c r="F299" s="4">
         <f t="shared" si="9"/>
-        <v>319.00300000000061</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+        <v>358.80000000000291</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="5"/>
       <c r="B300" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C300" s="4">
-        <v>21483.082999999999</v>
+        <v>21617.8</v>
       </c>
       <c r="D300" s="4">
         <f t="shared" si="8"/>
-        <v>21309.544000000002</v>
+        <v>21440.9</v>
       </c>
       <c r="E300">
         <v>298</v>
       </c>
       <c r="F300" s="4">
         <f t="shared" si="9"/>
-        <v>173.53899999999703</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+        <v>176.89999999999782</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="5"/>
       <c r="B301" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C301" s="4">
-        <v>21847.601999999999</v>
+        <v>21988.7</v>
       </c>
       <c r="D301" s="4">
         <f t="shared" si="8"/>
-        <v>21483.082999999999</v>
+        <v>21617.8</v>
       </c>
       <c r="E301">
         <v>299</v>
       </c>
       <c r="F301" s="4">
         <f t="shared" si="9"/>
-        <v>364.51900000000023</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+        <v>370.90000000000146</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>2022</v>
       </c>
@@ -7510,81 +7531,81 @@
         <v>3</v>
       </c>
       <c r="C302" s="4">
-        <v>21738.870999999999</v>
+        <v>21932.7</v>
       </c>
       <c r="D302" s="4">
         <f t="shared" si="8"/>
-        <v>21847.601999999999</v>
+        <v>21988.7</v>
       </c>
       <c r="E302">
         <v>300</v>
       </c>
       <c r="F302" s="4">
         <f t="shared" si="9"/>
-        <v>-108.73099999999977</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-56</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="5"/>
       <c r="B303" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C303" s="4">
-        <v>21708.16</v>
+        <v>21967</v>
       </c>
       <c r="D303" s="4">
         <f t="shared" si="8"/>
-        <v>21738.870999999999</v>
+        <v>21932.7</v>
       </c>
       <c r="E303">
         <v>301</v>
       </c>
       <c r="F303" s="4">
         <f t="shared" si="9"/>
-        <v>-30.710999999999331</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+        <v>34.299999999999272</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="5"/>
       <c r="B304" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C304" s="4">
-        <v>21851.133999999998</v>
+        <v>22125.599999999999</v>
       </c>
       <c r="D304" s="4">
         <f t="shared" si="8"/>
-        <v>21708.16</v>
+        <v>21967</v>
       </c>
       <c r="E304">
         <v>302</v>
       </c>
       <c r="F304" s="4">
         <f t="shared" si="9"/>
-        <v>142.97399999999834</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+        <v>158.59999999999854</v>
+      </c>
+    </row>
+    <row r="305" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A305" s="5"/>
       <c r="B305" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C305" s="4">
-        <v>21989.981</v>
+        <v>22278.3</v>
       </c>
       <c r="D305" s="4">
         <f t="shared" si="8"/>
-        <v>21851.133999999998</v>
+        <v>22125.599999999999</v>
       </c>
       <c r="E305">
         <v>303</v>
       </c>
       <c r="F305" s="4">
         <f t="shared" si="9"/>
-        <v>138.84700000000157</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+        <v>152.70000000000073</v>
+      </c>
+    </row>
+    <row r="306" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>2023</v>
       </c>
@@ -7592,84 +7613,300 @@
         <v>3</v>
       </c>
       <c r="C306" s="4">
-        <v>22112.329000000002</v>
+        <v>22439.599999999999</v>
       </c>
       <c r="D306" s="4">
         <f t="shared" si="8"/>
-        <v>21989.981</v>
+        <v>22278.3</v>
       </c>
       <c r="E306">
         <v>304</v>
       </c>
       <c r="F306" s="4">
         <f t="shared" si="9"/>
-        <v>122.34800000000178</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+        <v>161.29999999999927</v>
+      </c>
+    </row>
+    <row r="307" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A307" s="5"/>
       <c r="B307" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C307" s="4">
-        <v>22225.35</v>
+        <v>22580.5</v>
       </c>
       <c r="D307" s="4">
         <f t="shared" si="8"/>
-        <v>22112.329000000002</v>
+        <v>22439.599999999999</v>
       </c>
       <c r="E307">
         <v>305</v>
       </c>
       <c r="F307" s="4">
         <f t="shared" si="9"/>
-        <v>113.020999999997</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+        <v>140.90000000000146</v>
+      </c>
+    </row>
+    <row r="308" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A308" s="5"/>
       <c r="B308" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C308" s="4">
-        <v>22490.691999999999</v>
+        <v>22841</v>
       </c>
       <c r="D308" s="4">
         <f t="shared" si="8"/>
-        <v>22225.35</v>
+        <v>22580.5</v>
       </c>
       <c r="E308">
         <v>306</v>
       </c>
       <c r="F308" s="4">
         <f t="shared" si="9"/>
-        <v>265.34200000000055</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+        <v>260.5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A309" s="5"/>
       <c r="B309" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C309" s="4">
-        <v>22672.859</v>
+        <v>23033.8</v>
       </c>
       <c r="D309" s="4">
         <f t="shared" si="8"/>
-        <v>22490.691999999999</v>
+        <v>22841</v>
       </c>
       <c r="E309">
         <v>307</v>
       </c>
       <c r="F309" s="4">
         <f t="shared" si="9"/>
-        <v>182.16700000000128</v>
+        <v>192.79999999999927</v>
+      </c>
+    </row>
+    <row r="310" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A310" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C310" s="4">
+        <v>23082.1</v>
+      </c>
+      <c r="D310" s="4">
+        <f t="shared" si="8"/>
+        <v>23033.8</v>
+      </c>
+      <c r="E310">
+        <v>308</v>
+      </c>
+      <c r="F310" s="4">
+        <f t="shared" si="9"/>
+        <v>48.299999999999272</v>
+      </c>
+    </row>
+    <row r="311" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A311" s="5"/>
+      <c r="B311" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" s="4">
+        <v>23286.5</v>
+      </c>
+      <c r="D311" s="4">
+        <f t="shared" si="8"/>
+        <v>23082.1</v>
+      </c>
+      <c r="E311">
+        <v>309</v>
+      </c>
+      <c r="F311" s="4">
+        <f t="shared" si="9"/>
+        <v>204.40000000000146</v>
+      </c>
+    </row>
+    <row r="312" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A312" s="5"/>
+      <c r="B312" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C312" s="4">
+        <v>23478.6</v>
+      </c>
+      <c r="D312" s="4">
+        <f t="shared" si="8"/>
+        <v>23286.5</v>
+      </c>
+      <c r="E312">
+        <v>310</v>
+      </c>
+      <c r="F312" s="4">
+        <f t="shared" si="9"/>
+        <v>192.09999999999854</v>
+      </c>
+      <c r="H312" s="12"/>
+      <c r="I312" s="12"/>
+      <c r="J312" s="12"/>
+      <c r="K312" s="12"/>
+      <c r="L312" s="12"/>
+      <c r="M312" s="12"/>
+      <c r="N312" s="12"/>
+      <c r="O312" s="12"/>
+      <c r="P312" s="12"/>
+      <c r="Q312" s="12"/>
+      <c r="R312" s="12"/>
+      <c r="S312" s="12"/>
+      <c r="T312" s="12"/>
+      <c r="U312" s="12"/>
+      <c r="V312" s="12"/>
+      <c r="W312" s="12"/>
+      <c r="X312" s="12"/>
+      <c r="Y312" s="12"/>
+      <c r="Z312" s="12"/>
+      <c r="AA312" s="12"/>
+      <c r="AB312" s="12"/>
+      <c r="AC312" s="12"/>
+      <c r="AD312" s="12"/>
+      <c r="AE312" s="12"/>
+      <c r="AF312" s="12"/>
+      <c r="AG312" s="12"/>
+      <c r="AH312" s="12"/>
+      <c r="AI312" s="12"/>
+      <c r="AJ312" s="12"/>
+    </row>
+    <row r="313" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A313" s="5"/>
+      <c r="B313" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C313" s="4">
+        <v>23586.5</v>
+      </c>
+      <c r="D313" s="4">
+        <f t="shared" si="8"/>
+        <v>23478.6</v>
+      </c>
+      <c r="E313">
+        <v>311</v>
+      </c>
+      <c r="F313" s="4">
+        <f t="shared" si="9"/>
+        <v>107.90000000000146</v>
+      </c>
+    </row>
+    <row r="314" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A314" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="4">
+        <v>23548.2</v>
+      </c>
+      <c r="D314" s="4">
+        <f t="shared" si="8"/>
+        <v>23586.5</v>
+      </c>
+      <c r="E314">
+        <v>312</v>
+      </c>
+      <c r="F314" s="4">
+        <f t="shared" si="9"/>
+        <v>-38.299999999999272</v>
+      </c>
+    </row>
+    <row r="315" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A315" s="5"/>
+      <c r="B315" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C315" s="4">
+        <v>23771</v>
+      </c>
+      <c r="D315" s="4">
+        <f t="shared" si="8"/>
+        <v>23548.2</v>
+      </c>
+      <c r="E315">
+        <v>313</v>
+      </c>
+      <c r="F315" s="4">
+        <f t="shared" si="9"/>
+        <v>222.79999999999927</v>
+      </c>
+    </row>
+    <row r="316" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A316" s="5"/>
+      <c r="B316" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C316" s="4">
+        <v>24026.799999999999</v>
+      </c>
+      <c r="D316" s="4">
+        <f t="shared" si="8"/>
+        <v>23771</v>
+      </c>
+      <c r="E316">
+        <v>314</v>
+      </c>
+      <c r="F316" s="4">
+        <f t="shared" si="9"/>
+        <v>255.79999999999927</v>
+      </c>
+    </row>
+    <row r="317" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A317" s="5"/>
+      <c r="B317" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C317" s="4">
+        <v>24055.7</v>
+      </c>
+      <c r="D317" s="4">
+        <f t="shared" si="8"/>
+        <v>24026.799999999999</v>
+      </c>
+      <c r="E317">
+        <v>315</v>
+      </c>
+      <c r="F317" s="4">
+        <f t="shared" si="9"/>
+        <v>28.900000000001455</v>
+      </c>
+    </row>
+    <row r="318" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A318" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C318" s="4">
+        <v>24180.400000000001</v>
+      </c>
+      <c r="D318" s="4">
+        <f t="shared" si="8"/>
+        <v>24055.7</v>
+      </c>
+      <c r="E318">
+        <v>316</v>
+      </c>
+      <c r="F318" s="4">
+        <f t="shared" si="9"/>
+        <v>124.70000000000073</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:I1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
@@ -7677,18 +7914,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4283677D-A716-486E-B4EA-C078314CADB9}">
-  <dimension ref="A1:I309"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I318"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.28515625" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7712,7 +7949,7 @@
       </c>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1947</v>
       </c>
@@ -7730,7 +7967,7 @@
         <v>-1.9419999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
@@ -7754,7 +7991,7 @@
         <v>-2.8730000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
         <v>5</v>
@@ -7780,7 +8017,7 @@
         <v>-3.427</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
         <v>6</v>
@@ -7804,7 +8041,7 @@
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1948</v>
       </c>
@@ -7826,7 +8063,7 @@
         <v>-0.79000000000087311</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="3" t="s">
         <v>4</v>
@@ -7846,7 +8083,7 @@
         <v>3.7780000000007021</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="3" t="s">
         <v>5</v>
@@ -7866,7 +8103,7 @@
         <v>-23.928000000000338</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="3" t="s">
         <v>6</v>
@@ -7886,7 +8123,7 @@
         <v>-10.485999999999876</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1949</v>
       </c>
@@ -7908,7 +8145,7 @@
         <v>-34.151000000000295</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="3" t="s">
         <v>4</v>
@@ -7928,7 +8165,7 @@
         <v>23.878000000000611</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="3" t="s">
         <v>5</v>
@@ -7948,7 +8185,7 @@
         <v>30.974999999999454</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3" t="s">
         <v>6</v>
@@ -7968,7 +8205,7 @@
         <v>-42.367999999999938</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>1950</v>
       </c>
@@ -7990,7 +8227,7 @@
         <v>107.82400000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="3" t="s">
         <v>4</v>
@@ -8010,7 +8247,7 @@
         <v>-17.173999999999978</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="3" t="s">
         <v>5</v>
@@ -8030,7 +8267,7 @@
         <v>21.867000000000189</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -8050,7 +8287,7 @@
         <v>-45.358000000000175</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>1951</v>
       </c>
@@ -8072,7 +8309,7 @@
         <v>-13.333999999999833</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
         <v>4</v>
@@ -8092,7 +8329,7 @@
         <v>10.177999999999884</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="3" t="s">
         <v>5</v>
@@ -8112,7 +8349,7 @@
         <v>9.4299999999998363</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="3" t="s">
         <v>6</v>
@@ -8132,7 +8369,7 @@
         <v>-48.463999999999942</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>1952</v>
       </c>
@@ -8154,7 +8391,7 @@
         <v>22.901000000000295</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="3" t="s">
         <v>4</v>
@@ -8174,7 +8411,7 @@
         <v>-22.952000000000226</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
         <v>5</v>
@@ -8194,7 +8431,7 @@
         <v>13.87099999999964</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="3" t="s">
         <v>6</v>
@@ -8214,7 +8451,7 @@
         <v>70.707000000000335</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>1953</v>
       </c>
@@ -8236,7 +8473,7 @@
         <v>-37.553999999999633</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="3" t="s">
         <v>4</v>
@@ -8256,7 +8493,7 @@
         <v>-30.475000000000364</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="3" t="s">
         <v>5</v>
@@ -8276,7 +8513,7 @@
         <v>-38.816000000000258</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
         <v>6</v>
@@ -8296,7 +8533,7 @@
         <v>-27.518999999999778</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>1954</v>
       </c>
@@ -8318,7 +8555,7 @@
         <v>30.287000000000262</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="3" t="s">
         <v>4</v>
@@ -8338,7 +8575,7 @@
         <v>16.765999999999622</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="3" t="s">
         <v>5</v>
@@ -8358,7 +8595,7 @@
         <v>29.064000000000306</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="3" t="s">
         <v>6</v>
@@ -8378,7 +8615,7 @@
         <v>24.192999999999756</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>1955</v>
       </c>
@@ -8400,7 +8637,7 @@
         <v>27.524000000000342</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="3" t="s">
         <v>4</v>
@@ -8420,7 +8657,7 @@
         <v>-34.730000000000473</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="3" t="s">
         <v>5</v>
@@ -8440,7 +8677,7 @@
         <v>-7.694999999999709</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="3" t="s">
         <v>6</v>
@@ -8460,7 +8697,7 @@
         <v>-22.779999999999745</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>1956</v>
       </c>
@@ -8482,7 +8719,7 @@
         <v>-30.835000000000491</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="3" t="s">
         <v>4</v>
@@ -8502,7 +8739,7 @@
         <v>37.91800000000012</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="3" t="s">
         <v>5</v>
@@ -8522,7 +8759,7 @@
         <v>-28.592000000000098</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="3" t="s">
         <v>6</v>
@@ -8542,7 +8779,7 @@
         <v>54.516000000000531</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>1957</v>
       </c>
@@ -8564,7 +8801,7 @@
         <v>-31.255000000000564</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="3" t="s">
         <v>4</v>
@@ -8584,7 +8821,7 @@
         <v>-27.481999999999971</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="3" t="s">
         <v>5</v>
@@ -8604,7 +8841,7 @@
         <v>38.457000000000335</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" s="3" t="s">
         <v>6</v>
@@ -8624,7 +8861,7 @@
         <v>-64.908000000000357</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>1958</v>
       </c>
@@ -8646,7 +8883,7 @@
         <v>-49.677999999999429</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="3" t="s">
         <v>4</v>
@@ -8666,7 +8903,7 @@
         <v>103.66999999999962</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="3" t="s">
         <v>5</v>
@@ -8686,7 +8923,7 @@
         <v>52.159999999999854</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="3" t="s">
         <v>6</v>
@@ -8706,7 +8943,7 @@
         <v>2.4880000000002838</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>1959</v>
       </c>
@@ -8728,7 +8965,7 @@
         <v>-12.051000000000386</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="3" t="s">
         <v>4</v>
@@ -8748,7 +8985,7 @@
         <v>12.441000000000258</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="3" t="s">
         <v>5</v>
@@ -8768,7 +9005,7 @@
         <v>-73.148000000000138</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="3" t="s">
         <v>6</v>
@@ -8788,7 +9025,7 @@
         <v>7.3850000000002183</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>1960</v>
       </c>
@@ -8810,7 +9047,7 @@
         <v>67.574000000000069</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="3" t="s">
         <v>4</v>
@@ -8830,7 +9067,7 @@
         <v>-96.284000000000106</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="3" t="s">
         <v>5</v>
@@ -8850,7 +9087,7 @@
         <v>36.074000000000069</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="B57" s="3" t="s">
         <v>6</v>
@@ -8870,7 +9107,7 @@
         <v>-62.246000000000549</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>1961</v>
       </c>
@@ -8892,7 +9129,7 @@
         <v>68.532000000000608</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
       <c r="B59" s="3" t="s">
         <v>4</v>
@@ -8912,7 +9149,7 @@
         <v>35.893000000000029</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="3" t="s">
         <v>5</v>
@@ -8932,7 +9169,7 @@
         <v>8.9129999999995562</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="3" t="s">
         <v>6</v>
@@ -8952,7 +9189,7 @@
         <v>2.8060000000004948</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>1962</v>
       </c>
@@ -8974,7 +9211,7 @@
         <v>-5.1790000000005421</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="B63" s="3" t="s">
         <v>4</v>
@@ -8994,7 +9231,7 @@
         <v>-31.855999999999767</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="B64" s="3" t="s">
         <v>5</v>
@@ -9014,7 +9251,7 @@
         <v>12.625</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="B65" s="3" t="s">
         <v>6</v>
@@ -9034,7 +9271,7 @@
         <v>-33.981999999999971</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>1963</v>
       </c>
@@ -9056,7 +9293,7 @@
         <v>29.416000000000167</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="3" t="s">
         <v>4</v>
@@ -9076,7 +9313,7 @@
         <v>1.6399999999998727</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" s="3" t="s">
         <v>5</v>
@@ -9096,7 +9333,7 @@
         <v>42.871000000000095</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
       <c r="B69" s="3" t="s">
         <v>6</v>
@@ -9116,7 +9353,7 @@
         <v>-60.180000000000291</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>1964</v>
       </c>
@@ -9138,7 +9375,7 @@
         <v>59.014000000000124</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" s="3" t="s">
         <v>4</v>
@@ -9158,7 +9395,7 @@
         <v>-40.367000000000189</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" s="3" t="s">
         <v>5</v>
@@ -9178,7 +9415,7 @@
         <v>20.287000000000262</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" s="3" t="s">
         <v>6</v>
@@ -9198,7 +9435,7 @@
         <v>-52.197999999999411</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>1965</v>
       </c>
@@ -9220,7 +9457,7 @@
         <v>89.936999999998989</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" s="3" t="s">
         <v>4</v>
@@ -9240,7 +9477,7 @@
         <v>-47.950999999999112</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
       <c r="B76" s="3" t="s">
         <v>5</v>
@@ -9260,7 +9497,7 @@
         <v>43.087999999998829</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="B77" s="3" t="s">
         <v>6</v>
@@ -9280,7 +9517,7 @@
         <v>5.829000000000633</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>1966</v>
       </c>
@@ -9302,7 +9539,7 @@
         <v>8.399000000000342</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="3" t="s">
         <v>4</v>
@@ -9322,7 +9559,7 @@
         <v>-96.271999999999935</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" s="3" t="s">
         <v>5</v>
@@ -9342,7 +9579,7 @@
         <v>24.049999999999272</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
       <c r="B81" s="3" t="s">
         <v>6</v>
@@ -9362,7 +9599,7 @@
         <v>-0.9249999999992724</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>1967</v>
       </c>
@@ -9384,7 +9621,7 @@
         <v>3.4789999999993597</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="3" t="s">
         <v>4</v>
@@ -9404,7 +9641,7 @@
         <v>-39.773999999999432</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
       <c r="B84" s="3" t="s">
         <v>5</v>
@@ -9424,7 +9661,7 @@
         <v>43.11699999999928</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
       <c r="B85" s="3" t="s">
         <v>6</v>
@@ -9444,7 +9681,7 @@
         <v>-9.0199999999995271</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>1968</v>
       </c>
@@ -9466,7 +9703,7 @@
         <v>63.990999999999985</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
       <c r="B87" s="3" t="s">
         <v>4</v>
@@ -9486,7 +9723,7 @@
         <v>-16.595999999999549</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
       <c r="B88" s="3" t="s">
         <v>5</v>
@@ -9506,7 +9743,7 @@
         <v>-44.654000000000451</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
       <c r="B89" s="3" t="s">
         <v>6</v>
@@ -9526,7 +9763,7 @@
         <v>-19.472999999999956</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>1969</v>
       </c>
@@ -9548,7 +9785,7 @@
         <v>61.031999999999243</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
       <c r="B91" s="3" t="s">
         <v>4</v>
@@ -9568,7 +9805,7 @@
         <v>-65.356999999999061</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="3" t="s">
         <v>5</v>
@@ -9588,7 +9825,7 @@
         <v>18.947000000000116</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="3" t="s">
         <v>6</v>
@@ -9608,7 +9845,7 @@
         <v>-61.019000000001142</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>1970</v>
       </c>
@@ -9630,7 +9867,7 @@
         <v>18.140000000001237</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
       <c r="B95" s="3" t="s">
         <v>4</v>
@@ -9650,7 +9887,7 @@
         <v>15.415999999999258</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="3" t="s">
         <v>5</v>
@@ -9670,7 +9907,7 @@
         <v>41.401000000000749</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
       <c r="B97" s="3" t="s">
         <v>6</v>
@@ -9690,7 +9927,7 @@
         <v>-106.31800000000112</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>1971</v>
       </c>
@@ -9712,7 +9949,7 @@
         <v>201.35200000000077</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
       <c r="B99" s="3" t="s">
         <v>4</v>
@@ -9732,7 +9969,7 @@
         <v>-114.50699999999961</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
       <c r="B100" s="3" t="s">
         <v>5</v>
@@ -9752,7 +9989,7 @@
         <v>15.572999999999411</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
       <c r="B101" s="3" t="s">
         <v>6</v>
@@ -9772,7 +10009,7 @@
         <v>-32.052999999999884</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>1972</v>
       </c>
@@ -9794,7 +10031,7 @@
         <v>88.657000000000153</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
       <c r="B103" s="3" t="s">
         <v>4</v>
@@ -9814,7 +10051,7 @@
         <v>26.203999999999724</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
       <c r="B104" s="3" t="s">
         <v>5</v>
@@ -9834,7 +10071,7 @@
         <v>-73.436999999999898</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
       <c r="B105" s="3" t="s">
         <v>6</v>
@@ -9854,7 +10091,7 @@
         <v>42.981999999999971</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>1973</v>
       </c>
@@ -9876,7 +10113,7 @@
         <v>48.957999999999629</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
       <c r="B107" s="3" t="s">
         <v>4</v>
@@ -9896,7 +10133,7 @@
         <v>-80.361999999999171</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
       <c r="B108" s="3" t="s">
         <v>5</v>
@@ -9916,7 +10153,7 @@
         <v>-98.167000000000371</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
       <c r="B109" s="3" t="s">
         <v>6</v>
@@ -9936,7 +10173,7 @@
         <v>90.034999999999854</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>1974</v>
       </c>
@@ -9958,7 +10195,7 @@
         <v>-110.70300000000043</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
       <c r="B111" s="3" t="s">
         <v>4</v>
@@ -9978,7 +10215,7 @@
         <v>67.366000000000895</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
       <c r="B112" s="3" t="s">
         <v>5</v>
@@ -9998,7 +10235,7 @@
         <v>-72.266000000000531</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
       <c r="B113" s="3" t="s">
         <v>6</v>
@@ -10018,7 +10255,7 @@
         <v>34.259000000000015</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>1975</v>
       </c>
@@ -10040,7 +10277,7 @@
         <v>-49.914999999999964</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
       <c r="B115" s="3" t="s">
         <v>4</v>
@@ -10060,7 +10297,7 @@
         <v>116.00399999999991</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
       <c r="B116" s="3" t="s">
         <v>5</v>
@@ -10080,7 +10317,7 @@
         <v>60.141000000000531</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
       <c r="B117" s="3" t="s">
         <v>6</v>
@@ -10100,7 +10337,7 @@
         <v>-20.512000000000626</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>1976</v>
       </c>
@@ -10122,7 +10359,7 @@
         <v>56.915000000000873</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
       <c r="B119" s="3" t="s">
         <v>4</v>
@@ -10142,7 +10379,7 @@
         <v>-92.743000000001302</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
       <c r="B120" s="3" t="s">
         <v>5</v>
@@ -10162,7 +10399,7 @@
         <v>-11.505999999998494</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
       <c r="B121" s="3" t="s">
         <v>6</v>
@@ -10182,7 +10419,7 @@
         <v>11.411999999998443</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>1977</v>
       </c>
@@ -10204,7 +10441,7 @@
         <v>30.244000000001506</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
       <c r="B123" s="3" t="s">
         <v>4</v>
@@ -10224,7 +10461,7 @@
         <v>50.236999999999171</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
       <c r="B124" s="3" t="s">
         <v>5</v>
@@ -10244,7 +10481,7 @@
         <v>-6.7719999999999345</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
       <c r="B125" s="3" t="s">
         <v>6</v>
@@ -10264,7 +10501,7 @@
         <v>-119.85600000000068</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>1978</v>
       </c>
@@ -10286,7 +10523,7 @@
         <v>21.533000000001266</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
       <c r="B127" s="3" t="s">
         <v>4</v>
@@ -10306,7 +10543,7 @@
         <v>240.99199999999928</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
       <c r="B128" s="3" t="s">
         <v>5</v>
@@ -10326,7 +10563,7 @@
         <v>-191.66499999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
       <c r="B129" s="3" t="s">
         <v>6</v>
@@ -10346,7 +10583,7 @@
         <v>24.840000000000146</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>1979</v>
       </c>
@@ -10368,7 +10605,7 @@
         <v>-82.858000000000175</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
       <c r="B131" s="3" t="s">
         <v>4</v>
@@ -10388,7 +10625,7 @@
         <v>-5.25</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
       <c r="B132" s="3" t="s">
         <v>5</v>
@@ -10408,7 +10645,7 @@
         <v>46.100000000000364</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
       <c r="B133" s="3" t="s">
         <v>6</v>
@@ -10428,7 +10665,7 @@
         <v>-35.57300000000032</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>1980</v>
       </c>
@@ -10450,7 +10687,7 @@
         <v>4.7680000000000291</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
       <c r="B135" s="3" t="s">
         <v>4</v>
@@ -10470,7 +10707,7 @@
         <v>-174.28999999999996</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
       <c r="B136" s="3" t="s">
         <v>5</v>
@@ -10490,7 +10727,7 @@
         <v>142.72200000000066</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
       <c r="B137" s="3" t="s">
         <v>6</v>
@@ -10510,7 +10747,7 @@
         <v>142.47999999999865</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>1981</v>
       </c>
@@ -10532,7 +10769,7 @@
         <v>9.4110000000009677</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
       <c r="B139" s="3" t="s">
         <v>4</v>
@@ -10552,7 +10789,7 @@
         <v>-198.6220000000003</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
       <c r="B140" s="3" t="s">
         <v>5</v>
@@ -10572,7 +10809,7 @@
         <v>143.9369999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
       <c r="B141" s="3" t="s">
         <v>6</v>
@@ -10592,7 +10829,7 @@
         <v>-170.29699999999957</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>1982</v>
       </c>
@@ -10614,7 +10851,7 @@
         <v>-33.5</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
       <c r="B143" s="3" t="s">
         <v>4</v>
@@ -10634,7 +10871,7 @@
         <v>148.41799999999967</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
       <c r="B144" s="3" t="s">
         <v>5</v>
@@ -10654,7 +10891,7 @@
         <v>-61.29700000000048</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
       <c r="B145" s="3" t="s">
         <v>6</v>
@@ -10674,7 +10911,7 @@
         <v>30.937000000000808</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>1983</v>
       </c>
@@ -10696,7 +10933,7 @@
         <v>93.32799999999952</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
       <c r="B147" s="3" t="s">
         <v>4</v>
@@ -10716,7 +10953,7 @@
         <v>72.141000000000531</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
       <c r="B148" s="3" t="s">
         <v>5</v>
@@ -10736,7 +10973,7 @@
         <v>-17.100000000000364</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
       <c r="B149" s="3" t="s">
         <v>6</v>
@@ -10756,7 +10993,7 @@
         <v>9.7579999999998108</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>1984</v>
       </c>
@@ -10778,7 +11015,7 @@
         <v>-6.9949999999998909</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
       <c r="B151" s="3" t="s">
         <v>4</v>
@@ -10798,7 +11035,7 @@
         <v>-15.229999999999563</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
       <c r="B152" s="3" t="s">
         <v>5</v>
@@ -10818,7 +11055,7 @@
         <v>-60.028000000000247</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
       <c r="B153" s="3" t="s">
         <v>6</v>
@@ -10838,7 +11075,7 @@
         <v>-11.060999999999694</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>1985</v>
       </c>
@@ -10860,7 +11097,7 @@
         <v>12.886999999998807</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
       <c r="B155" s="3" t="s">
         <v>4</v>
@@ -10880,7 +11117,7 @@
         <v>-6.6539999999986321</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
       <c r="B156" s="3" t="s">
         <v>5</v>
@@ -10900,7 +11137,7 @@
         <v>55.46599999999853</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
       <c r="B157" s="3" t="s">
         <v>6</v>
@@ -10920,7 +11157,7 @@
         <v>-65.464999999998327</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>1986</v>
       </c>
@@ -10942,7 +11179,7 @@
         <v>16.970999999999549</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
       <c r="B159" s="3" t="s">
         <v>4</v>
@@ -10962,7 +11199,7 @@
         <v>-41.542000000001281</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
       <c r="B160" s="3" t="s">
         <v>5</v>
@@ -10982,7 +11219,7 @@
         <v>44.68000000000211</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
       <c r="B161" s="3" t="s">
         <v>6</v>
@@ -11002,7 +11239,7 @@
         <v>-36.485000000002401</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>1987</v>
       </c>
@@ -11024,7 +11261,7 @@
         <v>18.582000000002154</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
       <c r="B163" s="3" t="s">
         <v>4</v>
@@ -11044,7 +11281,7 @@
         <v>30.714999999998327</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
       <c r="B164" s="3" t="s">
         <v>5</v>
@@ -11064,7 +11301,7 @@
         <v>-18.120999999999185</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
       <c r="B165" s="3" t="s">
         <v>6</v>
@@ -11084,7 +11321,7 @@
         <v>78.540000000000873</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>1988</v>
       </c>
@@ -11106,7 +11343,7 @@
         <v>-109.13800000000083</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
       <c r="B167" s="3" t="s">
         <v>4</v>
@@ -11126,7 +11363,7 @@
         <v>74.921999999998661</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
       <c r="B168" s="3" t="s">
         <v>5</v>
@@ -11146,7 +11383,7 @@
         <v>-67.479999999997744</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
       <c r="B169" s="3" t="s">
         <v>6</v>
@@ -11166,7 +11403,7 @@
         <v>71.586999999999534</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>1989</v>
       </c>
@@ -11188,7 +11425,7 @@
         <v>-28.879000000000815</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
       <c r="B171" s="3" t="s">
         <v>4</v>
@@ -11208,7 +11445,7 @@
         <v>-23.752000000000407</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
       <c r="B172" s="3" t="s">
         <v>5</v>
@@ -11228,7 +11465,7 @@
         <v>-1.6329999999998108</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
       <c r="B173" s="3" t="s">
         <v>6</v>
@@ -11248,7 +11485,7 @@
         <v>-53.395999999998821</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>1990</v>
       </c>
@@ -11270,7 +11507,7 @@
         <v>89.079999999999927</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
       <c r="B175" s="3" t="s">
         <v>4</v>
@@ -11290,7 +11527,7 @@
         <v>-72.150000000001455</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
       <c r="B176" s="3" t="s">
         <v>5</v>
@@ -11310,7 +11547,7 @@
         <v>-29.7549999999992</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
       <c r="B177" s="3" t="s">
         <v>6</v>
@@ -11330,7 +11567,7 @@
         <v>-98.578999999999724</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>1991</v>
       </c>
@@ -11352,7 +11589,7 @@
         <v>45.076999999999316</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
       <c r="B179" s="3" t="s">
         <v>4</v>
@@ -11372,7 +11609,7 @@
         <v>124.38200000000143</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
       <c r="B180" s="3" t="s">
         <v>5</v>
@@ -11392,7 +11629,7 @@
         <v>-26.90900000000147</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
       <c r="B181" s="3" t="s">
         <v>6</v>
@@ -11412,7 +11649,7 @@
         <v>-15.550999999999476</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>1992</v>
       </c>
@@ -11434,7 +11671,7 @@
         <v>85.971999999999753</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
       <c r="B183" s="3" t="s">
         <v>4</v>
@@ -11454,7 +11691,7 @@
         <v>-10.111999999999171</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
       <c r="B184" s="3" t="s">
         <v>5</v>
@@ -11474,7 +11711,7 @@
         <v>-8.75</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
       <c r="B185" s="3" t="s">
         <v>6</v>
@@ -11494,7 +11731,7 @@
         <v>6.7309999999979482</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>1993</v>
       </c>
@@ -11516,7 +11753,7 @@
         <v>-91.347999999998137</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
       <c r="B187" s="3" t="s">
         <v>4</v>
@@ -11536,7 +11773,7 @@
         <v>43.944999999999709</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
       <c r="B188" s="3" t="s">
         <v>5</v>
@@ -11556,7 +11793,7 @@
         <v>-10.813000000000102</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
       <c r="B189" s="3" t="s">
         <v>6</v>
@@ -11576,7 +11813,7 @@
         <v>94.621999999999389</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>1994</v>
       </c>
@@ -11598,7 +11835,7 @@
         <v>-40.251999999998588</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
       <c r="B191" s="3" t="s">
         <v>4</v>
@@ -11618,7 +11855,7 @@
         <v>43.115999999999985</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
       <c r="B192" s="3" t="s">
         <v>5</v>
@@ -11638,7 +11875,7 @@
         <v>-83.43000000000211</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
       <c r="B193" s="3" t="s">
         <v>6</v>
@@ -11658,7 +11895,7 @@
         <v>62.941000000002532</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>1995</v>
       </c>
@@ -11680,7 +11917,7 @@
         <v>-87.737000000002809</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
       <c r="B195" s="3" t="s">
         <v>4</v>
@@ -11700,7 +11937,7 @@
         <v>-6.2489999999979773</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
       <c r="B196" s="3" t="s">
         <v>5</v>
@@ -11720,7 +11957,7 @@
         <v>62.818999999999505</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
       <c r="B197" s="3" t="s">
         <v>6</v>
@@ -11740,7 +11977,7 @@
         <v>-18.832000000000335</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>1996</v>
       </c>
@@ -11762,7 +11999,7 @@
         <v>8.5940000000009604</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
       <c r="B199" s="3" t="s">
         <v>4</v>
@@ -11782,7 +12019,7 @@
         <v>107.37099999999919</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
       <c r="B200" s="3" t="s">
         <v>5</v>
@@ -11802,7 +12039,7 @@
         <v>-87.798999999999069</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
       <c r="B201" s="3" t="s">
         <v>6</v>
@@ -11822,7 +12059,7 @@
         <v>17.78899999999885</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>1997</v>
       </c>
@@ -11844,7 +12081,7 @@
         <v>-46.014999999999418</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="5"/>
       <c r="B203" s="3" t="s">
         <v>4</v>
@@ -11864,7 +12101,7 @@
         <v>124.05199999999968</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="5"/>
       <c r="B204" s="3" t="s">
         <v>5</v>
@@ -11884,7 +12121,7 @@
         <v>-47.959999999999127</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="5"/>
       <c r="B205" s="3" t="s">
         <v>6</v>
@@ -11904,7 +12141,7 @@
         <v>-47.304000000000087</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>1998</v>
       </c>
@@ -11926,7 +12163,7 @@
         <v>19.761999999998807</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="5"/>
       <c r="B207" s="3" t="s">
         <v>4</v>
@@ -11946,7 +12183,7 @@
         <v>-8.6499999999996362</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="5"/>
       <c r="B208" s="3" t="s">
         <v>5</v>
@@ -11966,7 +12203,7 @@
         <v>43.816000000000713</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="5"/>
       <c r="B209" s="3" t="s">
         <v>6</v>
@@ -11986,7 +12223,7 @@
         <v>47.5049999999992</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>1999</v>
       </c>
@@ -12008,7 +12245,7 @@
         <v>-84.990999999999985</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="5"/>
       <c r="B211" s="3" t="s">
         <v>4</v>
@@ -12028,7 +12265,7 @@
         <v>-12.77599999999984</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="5"/>
       <c r="B212" s="3" t="s">
         <v>5</v>
@@ -12048,7 +12285,7 @@
         <v>66.872000000001208</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="5"/>
       <c r="B213" s="3" t="s">
         <v>6</v>
@@ -12068,7 +12305,7 @@
         <v>45.185999999997875</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>2000</v>
       </c>
@@ -12090,7 +12327,7 @@
         <v>-173.04199999999764</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="5"/>
       <c r="B215" s="3" t="s">
         <v>4</v>
@@ -12110,7 +12347,7 @@
         <v>202.59399999999732</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="5"/>
       <c r="B216" s="3" t="s">
         <v>5</v>
@@ -12130,7 +12367,7 @@
         <v>-238.35699999999815</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="5"/>
       <c r="B217" s="3" t="s">
         <v>6</v>
@@ -12150,7 +12387,7 @@
         <v>70.048999999999069</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>2001</v>
       </c>
@@ -12172,7 +12409,7 @@
         <v>-131.09799999999814</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="5"/>
       <c r="B219" s="3" t="s">
         <v>4</v>
@@ -12192,7 +12429,7 @@
         <v>135.21899999999732</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="5"/>
       <c r="B220" s="3" t="s">
         <v>5</v>
@@ -12212,7 +12449,7 @@
         <v>-145.75199999999859</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="5"/>
       <c r="B221" s="3" t="s">
         <v>6</v>
@@ -12232,7 +12469,7 @@
         <v>96.236000000000786</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>2002</v>
       </c>
@@ -12254,7 +12491,7 @@
         <v>80.152999999998428</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="5"/>
       <c r="B223" s="3" t="s">
         <v>4</v>
@@ -12274,7 +12511,7 @@
         <v>-31.147999999999229</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="5"/>
       <c r="B224" s="3" t="s">
         <v>5</v>
@@ -12294,7 +12531,7 @@
         <v>-29.278000000000247</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="5"/>
       <c r="B225" s="3" t="s">
         <v>6</v>
@@ -12314,7 +12551,7 @@
         <v>-40.837999999999738</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>2003</v>
       </c>
@@ -12336,7 +12573,7 @@
         <v>58.613999999999578</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="5"/>
       <c r="B227" s="3" t="s">
         <v>4</v>
@@ -12356,7 +12593,7 @@
         <v>52.864999999999782</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="5"/>
       <c r="B228" s="3" t="s">
         <v>5</v>
@@ -12376,7 +12613,7 @@
         <v>115.78900000000067</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="5"/>
       <c r="B229" s="3" t="s">
         <v>6</v>
@@ -12396,7 +12633,7 @@
         <v>-71.236999999999171</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>2004</v>
       </c>
@@ -12418,7 +12655,7 @@
         <v>-88.058000000000902</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="5"/>
       <c r="B231" s="3" t="s">
         <v>4</v>
@@ -12438,7 +12675,7 @@
         <v>32.25</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="5"/>
       <c r="B232" s="3" t="s">
         <v>5</v>
@@ -12458,7 +12695,7 @@
         <v>27.59900000000016</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="5"/>
       <c r="B233" s="3" t="s">
         <v>6</v>
@@ -12478,7 +12715,7 @@
         <v>12.49199999999837</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>2005</v>
       </c>
@@ -12500,7 +12737,7 @@
         <v>15.586000000002969</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="5"/>
       <c r="B235" s="3" t="s">
         <v>4</v>
@@ -12520,7 +12757,7 @@
         <v>-95.7920000000031</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="5"/>
       <c r="B236" s="3" t="s">
         <v>5</v>
@@ -12540,7 +12777,7 @@
         <v>46.750000000001819</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="5"/>
       <c r="B237" s="3" t="s">
         <v>6</v>
@@ -12560,7 +12797,7 @@
         <v>-35.657999999999447</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>2006</v>
       </c>
@@ -12582,7 +12819,7 @@
         <v>127.9539999999979</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="5"/>
       <c r="B239" s="3" t="s">
         <v>4</v>
@@ -12602,7 +12839,7 @@
         <v>-174.78499999999622</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="5"/>
       <c r="B240" s="3" t="s">
         <v>5</v>
@@ -12622,7 +12859,7 @@
         <v>-17.729000000002998</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="5"/>
       <c r="B241" s="3" t="s">
         <v>6</v>
@@ -12642,7 +12879,7 @@
         <v>116.54100000000108</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>2007</v>
       </c>
@@ -12664,7 +12901,7 @@
         <v>-91.304000000003725</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="5"/>
       <c r="B243" s="3" t="s">
         <v>4</v>
@@ -12684,7 +12921,7 @@
         <v>51.80000000000291</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="5"/>
       <c r="B244" s="3" t="s">
         <v>5</v>
@@ -12704,7 +12941,7 @@
         <v>-5.3509999999987485</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="5"/>
       <c r="B245" s="3" t="s">
         <v>6</v>
@@ -12724,7 +12961,7 @@
         <v>9.330999999998312</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>2008</v>
       </c>
@@ -12746,7 +12983,7 @@
         <v>-177.79199999999764</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="5"/>
       <c r="B247" s="3" t="s">
         <v>4</v>
@@ -12766,7 +13003,7 @@
         <v>172.47599999999875</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="5"/>
       <c r="B248" s="3" t="s">
         <v>5</v>
@@ -12786,7 +13023,7 @@
         <v>-189.28400000000329</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="5"/>
       <c r="B249" s="3" t="s">
         <v>6</v>
@@ -12806,7 +13043,7 @@
         <v>-279.94899999999689</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>2009</v>
       </c>
@@ -12828,7 +13065,7 @@
         <v>181.85700000000179</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="5"/>
       <c r="B251" s="3" t="s">
         <v>4</v>
@@ -12848,7 +13085,7 @@
         <v>157.97099999999773</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="5"/>
       <c r="B252" s="3" t="s">
         <v>5</v>
@@ -12868,7 +13105,7 @@
         <v>86.253000000000611</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="5"/>
       <c r="B253" s="3" t="s">
         <v>6</v>
@@ -12888,7 +13125,7 @@
         <v>119.33699999999953</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>2010</v>
       </c>
@@ -12910,7 +13147,7 @@
         <v>-96.517000000001644</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="5"/>
       <c r="B255" s="3" t="s">
         <v>4</v>
@@ -12930,7 +13167,7 @@
         <v>80.496000000002823</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="5"/>
       <c r="B256" s="3" t="s">
         <v>5</v>
@@ -12950,7 +13187,7 @@
         <v>-31.348000000001775</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="5"/>
       <c r="B257" s="3" t="s">
         <v>6</v>
@@ -12970,7 +13207,7 @@
         <v>-40.505999999997584</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>2011</v>
       </c>
@@ -12992,7 +13229,7 @@
         <v>-128.83000000000175</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="5"/>
       <c r="B259" s="3" t="s">
         <v>4</v>
@@ -13012,7 +13249,7 @@
         <v>154.71399999999994</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="5"/>
       <c r="B260" s="3" t="s">
         <v>5</v>
@@ -13032,7 +13269,7 @@
         <v>-118.28300000000309</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="5"/>
       <c r="B261" s="3" t="s">
         <v>6</v>
@@ -13052,7 +13289,7 @@
         <v>195.07100000000355</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>2012</v>
       </c>
@@ -13074,7 +13311,7 @@
         <v>-46.843000000000757</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="5"/>
       <c r="B263" s="3" t="s">
         <v>4</v>
@@ -13094,7 +13331,7 @@
         <v>-66.911999999996624</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="5"/>
       <c r="B264" s="3" t="s">
         <v>5</v>
@@ -13114,7 +13351,7 @@
         <v>-52.390000000003056</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="5"/>
       <c r="B265" s="3" t="s">
         <v>6</v>
@@ -13134,7 +13371,7 @@
         <v>-4.9230000000025029</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>2013</v>
       </c>
@@ -13156,7 +13393,7 @@
         <v>152.34600000000501</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="5"/>
       <c r="B267" s="3" t="s">
         <v>4</v>
@@ -13176,7 +13413,7 @@
         <v>-125.2770000000055</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="5"/>
       <c r="B268" s="3" t="s">
         <v>5</v>
@@ -13196,7 +13433,7 @@
         <v>103.50800000000527</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="5"/>
       <c r="B269" s="3" t="s">
         <v>6</v>
@@ -13216,7 +13453,7 @@
         <v>4.9179999999978463</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>2014</v>
       </c>
@@ -13238,7 +13475,7 @@
         <v>-217.87000000000262</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="5"/>
       <c r="B271" s="3" t="s">
         <v>4</v>
@@ -13258,7 +13495,7 @@
         <v>294.11000000000422</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="5"/>
       <c r="B272" s="3" t="s">
         <v>5</v>
@@ -13278,7 +13515,7 @@
         <v>-10.907000000002881</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="5"/>
       <c r="B273" s="3" t="s">
         <v>6</v>
@@ -13298,7 +13535,7 @@
         <v>-127.93999999999869</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>2015</v>
       </c>
@@ -13320,7 +13557,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="5"/>
       <c r="B275" s="3" t="s">
         <v>4</v>
@@ -13340,7 +13577,7 @@
         <v>-50.968000000000757</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="5"/>
       <c r="B276" s="3" t="s">
         <v>5</v>
@@ -13360,7 +13597,7 @@
         <v>-40.446999999996478</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="5"/>
       <c r="B277" s="3" t="s">
         <v>6</v>
@@ -13380,7 +13617,7 @@
         <v>-40.387000000006083</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>2016</v>
       </c>
@@ -13402,7 +13639,7 @@
         <v>74.696000000003551</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="5"/>
       <c r="B279" s="3" t="s">
         <v>4</v>
@@ -13422,7 +13659,7 @@
         <v>-48.465000000000146</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="5"/>
       <c r="B280" s="3" t="s">
         <v>5</v>
@@ -13442,7 +13679,7 @@
         <v>74.209999999999127</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="5"/>
       <c r="B281" s="3" t="s">
         <v>6</v>
@@ -13462,7 +13699,7 @@
         <v>-28.81499999999869</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>2017</v>
       </c>
@@ -13484,7 +13721,7 @@
         <v>-12.422999999998865</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="5"/>
       <c r="B283" s="3" t="s">
         <v>4</v>
@@ -13504,7 +13741,7 @@
         <v>14.614999999997963</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="5"/>
       <c r="B284" s="3" t="s">
         <v>5</v>
@@ -13524,7 +13761,7 @@
         <v>45.210999999999331</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="5"/>
       <c r="B285" s="3" t="s">
         <v>6</v>
@@ -13544,7 +13781,7 @@
         <v>67.769000000000233</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>2018</v>
       </c>
@@ -13566,7 +13803,7 @@
         <v>-59.860999999997148</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="5"/>
       <c r="B287" s="3" t="s">
         <v>4</v>
@@ -13586,7 +13823,7 @@
         <v>-55.326000000004569</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="5"/>
       <c r="B288" s="3" t="s">
         <v>5</v>
@@ -13606,7 +13843,7 @@
         <v>19.27900000000227</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="5"/>
       <c r="B289" s="3" t="s">
         <v>6</v>
@@ -13626,7 +13863,7 @@
         <v>-96.957999999998719</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>2019</v>
       </c>
@@ -13634,7 +13871,7 @@
         <v>3</v>
       </c>
       <c r="C290" s="4">
-        <v>110.27600000000166</v>
+        <v>126.72599999999875</v>
       </c>
       <c r="D290" s="4">
         <f t="shared" si="8"/>
@@ -13645,70 +13882,70 @@
       </c>
       <c r="F290" s="4">
         <f t="shared" si="9"/>
-        <v>81.556000000000495</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+        <v>98.005999999997584</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="5"/>
       <c r="B291" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C291" s="4">
-        <v>169.37799999999697</v>
+        <v>170.70000000000073</v>
       </c>
       <c r="D291" s="4">
         <f t="shared" si="8"/>
-        <v>110.27600000000166</v>
+        <v>126.72599999999875</v>
       </c>
       <c r="E291">
         <v>288</v>
       </c>
       <c r="F291" s="4">
         <f t="shared" si="9"/>
-        <v>59.101999999995314</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+        <v>43.974000000001979</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="5"/>
       <c r="B292" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C292" s="4">
-        <v>233.05299999999988</v>
+        <v>241</v>
       </c>
       <c r="D292" s="4">
         <f t="shared" si="8"/>
-        <v>169.37799999999697</v>
+        <v>170.70000000000073</v>
       </c>
       <c r="E292">
         <v>289</v>
       </c>
       <c r="F292" s="4">
         <f t="shared" si="9"/>
-        <v>63.67500000000291</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+        <v>70.299999999999272</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="5"/>
       <c r="B293" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C293" s="4">
-        <v>133.50700000000143</v>
+        <v>142.10000000000218</v>
       </c>
       <c r="D293" s="4">
         <f t="shared" si="8"/>
-        <v>233.05299999999988</v>
+        <v>241</v>
       </c>
       <c r="E293">
         <v>290</v>
       </c>
       <c r="F293" s="4">
         <f t="shared" si="9"/>
-        <v>-99.545999999998457</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-98.899999999997817</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>2020</v>
       </c>
@@ -13716,81 +13953,81 @@
         <v>3</v>
       </c>
       <c r="C294" s="4">
-        <v>-285.53499999999985</v>
+        <v>-276.20000000000073</v>
       </c>
       <c r="D294" s="4">
         <f t="shared" si="8"/>
-        <v>133.50700000000143</v>
+        <v>142.10000000000218</v>
       </c>
       <c r="E294">
         <v>291</v>
       </c>
       <c r="F294" s="4">
         <f t="shared" si="9"/>
-        <v>-419.04200000000128</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-418.30000000000291</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="5"/>
       <c r="B295" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C295" s="4">
-        <v>-1630.7229999999981</v>
+        <v>-1631.2000000000007</v>
       </c>
       <c r="D295" s="4">
         <f t="shared" si="8"/>
-        <v>-285.53499999999985</v>
+        <v>-276.20000000000073</v>
       </c>
       <c r="E295">
         <v>292</v>
       </c>
       <c r="F295" s="4">
         <f t="shared" si="9"/>
-        <v>-1345.1879999999983</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-1355</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="5"/>
       <c r="B296" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C296" s="4">
-        <v>1476.9549999999981</v>
+        <v>1480.9000000000015</v>
       </c>
       <c r="D296" s="4">
         <f t="shared" si="8"/>
-        <v>-1630.7229999999981</v>
+        <v>-1631.2000000000007</v>
       </c>
       <c r="E296">
         <v>293</v>
       </c>
       <c r="F296" s="4">
         <f t="shared" si="9"/>
-        <v>3107.6779999999962</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+        <v>3112.1000000000022</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="5"/>
       <c r="B297" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C297" s="4">
-        <v>212.34300000000076</v>
+        <v>233</v>
       </c>
       <c r="D297" s="4">
         <f t="shared" si="8"/>
-        <v>1476.9549999999981</v>
+        <v>1480.9000000000015</v>
       </c>
       <c r="E297">
         <v>294</v>
       </c>
       <c r="F297" s="4">
         <f t="shared" si="9"/>
-        <v>-1264.6119999999974</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-1247.9000000000015</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>2021</v>
       </c>
@@ -13798,81 +14035,81 @@
         <v>3</v>
       </c>
       <c r="C298" s="4">
-        <v>266.41300000000047</v>
+        <v>290.19999999999709</v>
       </c>
       <c r="D298" s="4">
         <f t="shared" si="8"/>
-        <v>212.34300000000076</v>
+        <v>233</v>
       </c>
       <c r="E298">
         <v>295</v>
       </c>
       <c r="F298" s="4">
         <f t="shared" si="9"/>
-        <v>54.069999999999709</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+        <v>57.19999999999709</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="5"/>
       <c r="B299" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C299" s="4">
-        <v>319.00300000000061</v>
+        <v>358.80000000000291</v>
       </c>
       <c r="D299" s="4">
         <f t="shared" si="8"/>
-        <v>266.41300000000047</v>
+        <v>290.19999999999709</v>
       </c>
       <c r="E299">
         <v>296</v>
       </c>
       <c r="F299" s="4">
         <f t="shared" si="9"/>
-        <v>52.590000000000146</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+        <v>68.600000000005821</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="5"/>
       <c r="B300" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C300" s="4">
-        <v>173.53899999999703</v>
+        <v>176.89999999999782</v>
       </c>
       <c r="D300" s="4">
         <f t="shared" si="8"/>
-        <v>319.00300000000061</v>
+        <v>358.80000000000291</v>
       </c>
       <c r="E300">
         <v>297</v>
       </c>
       <c r="F300" s="4">
         <f t="shared" si="9"/>
-        <v>-145.46400000000358</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-181.90000000000509</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="5"/>
       <c r="B301" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C301" s="4">
-        <v>364.51900000000023</v>
+        <v>370.90000000000146</v>
       </c>
       <c r="D301" s="4">
         <f t="shared" si="8"/>
-        <v>173.53899999999703</v>
+        <v>176.89999999999782</v>
       </c>
       <c r="E301">
         <v>298</v>
       </c>
       <c r="F301" s="4">
         <f t="shared" si="9"/>
-        <v>190.9800000000032</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+        <v>194.00000000000364</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>2022</v>
       </c>
@@ -13880,81 +14117,81 @@
         <v>3</v>
       </c>
       <c r="C302" s="4">
-        <v>-108.73099999999977</v>
+        <v>-56</v>
       </c>
       <c r="D302" s="4">
         <f t="shared" si="8"/>
-        <v>364.51900000000023</v>
+        <v>370.90000000000146</v>
       </c>
       <c r="E302">
         <v>299</v>
       </c>
       <c r="F302" s="4">
         <f t="shared" si="9"/>
-        <v>-473.25</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-426.90000000000146</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="5"/>
       <c r="B303" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C303" s="4">
-        <v>-30.710999999999331</v>
+        <v>34.299999999999272</v>
       </c>
       <c r="D303" s="4">
         <f t="shared" si="8"/>
-        <v>-108.73099999999977</v>
+        <v>-56</v>
       </c>
       <c r="E303">
         <v>300</v>
       </c>
       <c r="F303" s="4">
         <f t="shared" si="9"/>
-        <v>78.020000000000437</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+        <v>90.299999999999272</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="5"/>
       <c r="B304" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C304" s="4">
-        <v>142.97399999999834</v>
+        <v>158.59999999999854</v>
       </c>
       <c r="D304" s="4">
         <f t="shared" si="8"/>
-        <v>-30.710999999999331</v>
+        <v>34.299999999999272</v>
       </c>
       <c r="E304">
         <v>301</v>
       </c>
       <c r="F304" s="4">
         <f t="shared" si="9"/>
-        <v>173.68499999999767</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+        <v>124.29999999999927</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="5"/>
       <c r="B305" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C305" s="4">
-        <v>138.84700000000157</v>
+        <v>152.70000000000073</v>
       </c>
       <c r="D305" s="4">
         <f t="shared" si="8"/>
-        <v>142.97399999999834</v>
+        <v>158.59999999999854</v>
       </c>
       <c r="E305">
         <v>302</v>
       </c>
       <c r="F305" s="4">
         <f t="shared" si="9"/>
-        <v>-4.1269999999967695</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-5.8999999999978172</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>2023</v>
       </c>
@@ -13962,84 +14199,271 @@
         <v>3</v>
       </c>
       <c r="C306" s="4">
-        <v>122.34800000000178</v>
+        <v>161.29999999999927</v>
       </c>
       <c r="D306" s="4">
         <f t="shared" si="8"/>
-        <v>138.84700000000157</v>
+        <v>152.70000000000073</v>
       </c>
       <c r="E306">
         <v>303</v>
       </c>
       <c r="F306" s="4">
         <f t="shared" si="9"/>
-        <v>-16.498999999999796</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+        <v>8.5999999999985448</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="5"/>
       <c r="B307" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C307" s="4">
-        <v>113.020999999997</v>
+        <v>140.90000000000146</v>
       </c>
       <c r="D307" s="4">
         <f t="shared" si="8"/>
-        <v>122.34800000000178</v>
+        <v>161.29999999999927</v>
       </c>
       <c r="E307">
         <v>304</v>
       </c>
       <c r="F307" s="4">
         <f t="shared" si="9"/>
-        <v>-9.327000000004773</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+        <v>-20.399999999997817</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="5"/>
       <c r="B308" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C308" s="4">
-        <v>265.34200000000055</v>
+        <v>260.5</v>
       </c>
       <c r="D308" s="4">
         <f t="shared" si="8"/>
-        <v>113.020999999997</v>
+        <v>140.90000000000146</v>
       </c>
       <c r="E308">
         <v>305</v>
       </c>
       <c r="F308" s="4">
         <f t="shared" si="9"/>
-        <v>152.32100000000355</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+        <v>119.59999999999854</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="5"/>
       <c r="B309" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C309" s="4">
-        <v>182.16700000000128</v>
+        <v>192.79999999999927</v>
       </c>
       <c r="D309" s="4">
         <f t="shared" si="8"/>
-        <v>265.34200000000055</v>
+        <v>260.5</v>
       </c>
       <c r="E309">
         <v>306</v>
       </c>
       <c r="F309" s="4">
         <f t="shared" si="9"/>
-        <v>-83.174999999999272</v>
+        <v>-67.700000000000728</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C310" s="4">
+        <v>48.299999999999272</v>
+      </c>
+      <c r="D310" s="4">
+        <f t="shared" ref="D310:D318" si="10">C309</f>
+        <v>192.79999999999927</v>
+      </c>
+      <c r="E310">
+        <v>307</v>
+      </c>
+      <c r="F310" s="4">
+        <f t="shared" ref="F310:F318" si="11">C310-D310</f>
+        <v>-144.5</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" s="5"/>
+      <c r="B311" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" s="4">
+        <v>204.40000000000146</v>
+      </c>
+      <c r="D311" s="4">
+        <f t="shared" si="10"/>
+        <v>48.299999999999272</v>
+      </c>
+      <c r="E311">
+        <v>308</v>
+      </c>
+      <c r="F311" s="4">
+        <f t="shared" si="11"/>
+        <v>156.10000000000218</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" s="5"/>
+      <c r="B312" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C312" s="4">
+        <v>192.09999999999854</v>
+      </c>
+      <c r="D312" s="4">
+        <f t="shared" si="10"/>
+        <v>204.40000000000146</v>
+      </c>
+      <c r="E312">
+        <v>309</v>
+      </c>
+      <c r="F312" s="4">
+        <f t="shared" si="11"/>
+        <v>-12.30000000000291</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" s="5"/>
+      <c r="B313" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C313" s="4">
+        <v>107.90000000000146</v>
+      </c>
+      <c r="D313" s="4">
+        <f t="shared" si="10"/>
+        <v>192.09999999999854</v>
+      </c>
+      <c r="E313">
+        <v>310</v>
+      </c>
+      <c r="F313" s="4">
+        <f t="shared" si="11"/>
+        <v>-84.19999999999709</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="4">
+        <v>-38.299999999999272</v>
+      </c>
+      <c r="D314" s="4">
+        <f t="shared" si="10"/>
+        <v>107.90000000000146</v>
+      </c>
+      <c r="E314">
+        <v>311</v>
+      </c>
+      <c r="F314" s="4">
+        <f t="shared" si="11"/>
+        <v>-146.20000000000073</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" s="5"/>
+      <c r="B315" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C315" s="4">
+        <v>222.79999999999927</v>
+      </c>
+      <c r="D315" s="4">
+        <f t="shared" si="10"/>
+        <v>-38.299999999999272</v>
+      </c>
+      <c r="E315">
+        <v>312</v>
+      </c>
+      <c r="F315" s="4">
+        <f t="shared" si="11"/>
+        <v>261.09999999999854</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" s="5"/>
+      <c r="B316" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C316" s="4">
+        <v>255.79999999999927</v>
+      </c>
+      <c r="D316" s="4">
+        <f t="shared" si="10"/>
+        <v>222.79999999999927</v>
+      </c>
+      <c r="E316">
+        <v>313</v>
+      </c>
+      <c r="F316" s="4">
+        <f t="shared" si="11"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" s="5"/>
+      <c r="B317" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C317" s="4">
+        <v>28.900000000001455</v>
+      </c>
+      <c r="D317" s="4">
+        <f t="shared" si="10"/>
+        <v>255.79999999999927</v>
+      </c>
+      <c r="E317">
+        <v>314</v>
+      </c>
+      <c r="F317" s="4">
+        <f t="shared" si="11"/>
+        <v>-226.89999999999782</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C318" s="4">
+        <v>124.70000000000073</v>
+      </c>
+      <c r="D318" s="4">
+        <f t="shared" si="10"/>
+        <v>28.900000000001455</v>
+      </c>
+      <c r="E318">
+        <v>315</v>
+      </c>
+      <c r="F318" s="4">
+        <f t="shared" si="11"/>
+        <v>95.799999999999272</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:I1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>